--- a/воры/удаляем_часть1.xlsx
+++ b/воры/удаляем_часть1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\воры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD61879-CDBB-4EBA-8637-11C43081BAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2658F520-B93F-443E-B5C1-6A3F19A05103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="286">
   <si>
     <t>Артикул</t>
   </si>
@@ -64,42 +64,6 @@
   </si>
   <si>
     <t>путь к photoshop</t>
-  </si>
-  <si>
-    <t>Термонаклейка Котенок с шариком сердечко</t>
-  </si>
-  <si>
-    <t>Термонаклейка Сейлор Мун Sailor Moon голубой фон</t>
-  </si>
-  <si>
-    <t>Термонаклейка Марвел супергерои 4 верт фона</t>
-  </si>
-  <si>
-    <t>Термонаклейка Человек Паук круг красный синий</t>
-  </si>
-  <si>
-    <t>Термонаклейка Лев Краски Дизайн</t>
-  </si>
-  <si>
-    <t>Термонаклейка Эльза Холодное сердце синий круг</t>
-  </si>
-  <si>
-    <t>Термонаклейка Динозавр в очках играет на гитаре</t>
-  </si>
-  <si>
-    <t>Термонаклейка Щенячий патруль 2 Маршал Крепыш</t>
-  </si>
-  <si>
-    <t>Термонаклейка Миньон с бананами</t>
-  </si>
-  <si>
-    <t>Термонаклейка Жирафвыглядывает замок одежды</t>
-  </si>
-  <si>
-    <t>Термонаклейка Единорог с ромашкой сердечки</t>
-  </si>
-  <si>
-    <t>Термонаклейка Динозавр в очках ест бургер</t>
   </si>
   <si>
     <t>Термонаклейка Спанч Боб и друзья</t>
@@ -1329,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P279"/>
+  <dimension ref="A1:P267"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.140625" style="3" customWidth="1"/>
@@ -1377,13 +1341,13 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>12</v>
@@ -1394,25 +1358,34 @@
         <v>13</v>
       </c>
       <c r="B2" s="11">
-        <v>1506319215</v>
+        <v>1506319347</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2871997019</v>
       </c>
       <c r="E2" s="3">
-        <v>3130414626</v>
+        <v>3171275620</v>
       </c>
       <c r="F2" s="3">
-        <v>4723914630</v>
+        <v>3686479075</v>
       </c>
       <c r="G2" s="3">
-        <v>2898639844</v>
+        <v>4723913286</v>
       </c>
       <c r="H2" s="3">
-        <v>4561084964</v>
+        <v>2898635656</v>
       </c>
       <c r="I2" s="3">
-        <v>2873302064</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>294</v>
+        <v>4445002255</v>
+      </c>
+      <c r="J2" s="3">
+        <v>4561106321</v>
+      </c>
+      <c r="K2" s="3">
+        <v>2873298548</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -1420,22 +1393,16 @@
         <v>14</v>
       </c>
       <c r="B3" s="11">
-        <v>1506331468</v>
+        <v>1506320185</v>
       </c>
       <c r="C3" s="3">
-        <v>4362036238</v>
+        <v>3939763279</v>
       </c>
       <c r="D3" s="3">
-        <v>3795490786</v>
-      </c>
-      <c r="E3" s="3">
-        <v>3939771365</v>
-      </c>
-      <c r="F3" s="3">
-        <v>4724082672</v>
+        <v>3795490035</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -1443,34 +1410,13 @@
         <v>15</v>
       </c>
       <c r="B4" s="11">
-        <v>1506319337</v>
+        <v>1506331467</v>
       </c>
       <c r="C4" s="3">
-        <v>2872001630</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2963303304</v>
-      </c>
-      <c r="E4" s="3">
-        <v>3171275378</v>
-      </c>
-      <c r="F4" s="3">
-        <v>3130414764</v>
-      </c>
-      <c r="G4" s="3">
-        <v>2873297917</v>
-      </c>
-      <c r="H4" s="3">
-        <v>4723914754</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2898635636</v>
-      </c>
-      <c r="J4" s="3">
-        <v>4561091170</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>295</v>
+        <v>3678859195</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -1478,16 +1424,34 @@
         <v>16</v>
       </c>
       <c r="B5" s="11">
-        <v>1506319420</v>
-      </c>
-      <c r="C5" s="3">
-        <v>4723914321</v>
+        <v>1506372679</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2872000462</v>
       </c>
       <c r="D5" s="3">
-        <v>4561107576</v>
+        <v>2963301693</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3171276035</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3130413920</v>
+      </c>
+      <c r="G5" s="3">
+        <v>4723913926</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2898636763</v>
+      </c>
+      <c r="I5" s="3">
+        <v>4561091741</v>
+      </c>
+      <c r="J5" s="3">
+        <v>2873299334</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -1495,13 +1459,22 @@
         <v>17</v>
       </c>
       <c r="B6" s="11">
-        <v>1506331166</v>
+        <v>1522021181</v>
       </c>
       <c r="C6" s="3">
-        <v>3939771024</v>
+        <v>4420197936</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4353534394</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3939765424</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3795491581</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -1509,34 +1482,16 @@
         <v>18</v>
       </c>
       <c r="B7" s="11">
-        <v>1506319362</v>
+        <v>1522019560</v>
       </c>
       <c r="C7" s="3">
-        <v>2871997012</v>
+        <v>3939760105</v>
       </c>
       <c r="D7" s="3">
-        <v>2963300612</v>
-      </c>
-      <c r="E7" s="3">
-        <v>3171275548</v>
-      </c>
-      <c r="F7" s="3">
-        <v>3130417799</v>
-      </c>
-      <c r="G7" s="3">
-        <v>4723915716</v>
-      </c>
-      <c r="H7" s="3">
-        <v>2898638016</v>
-      </c>
-      <c r="I7" s="3">
-        <v>4561088092</v>
-      </c>
-      <c r="J7" s="3">
-        <v>2873299691</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>294</v>
+        <v>3939760105</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -1544,34 +1499,22 @@
         <v>19</v>
       </c>
       <c r="B8" s="11">
-        <v>1506319597</v>
+        <v>1522019577</v>
       </c>
       <c r="C8" s="3">
-        <v>2871996672</v>
+        <v>4353522509</v>
       </c>
       <c r="D8" s="3">
-        <v>2963303143</v>
+        <v>3795489493</v>
       </c>
       <c r="E8" s="3">
-        <v>3171275710</v>
+        <v>4420198417</v>
       </c>
       <c r="F8" s="3">
-        <v>3686477892</v>
-      </c>
-      <c r="G8" s="3">
-        <v>4723913880</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2898634856</v>
-      </c>
-      <c r="I8" s="3">
-        <v>4561107656</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2873297952</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>295</v>
+        <v>3678858448</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -1579,37 +1522,16 @@
         <v>20</v>
       </c>
       <c r="B9" s="11">
-        <v>1506319229</v>
+        <v>1522021741</v>
       </c>
       <c r="C9" s="3">
-        <v>2871999964</v>
+        <v>3795490630</v>
       </c>
       <c r="D9" s="3">
-        <v>2963302135</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3171275735</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3130418436</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2873298144</v>
-      </c>
-      <c r="H9" s="3">
-        <v>4723914435</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2898633481</v>
-      </c>
-      <c r="J9" s="3">
-        <v>4444955356</v>
-      </c>
-      <c r="K9" s="3">
-        <v>4561101994</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>295</v>
+        <v>3939763988</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -1617,28 +1539,19 @@
         <v>21</v>
       </c>
       <c r="B10" s="11">
-        <v>1506319088</v>
+        <v>1522019667</v>
       </c>
       <c r="C10" s="3">
-        <v>2963302285</v>
+        <v>4420199383</v>
       </c>
       <c r="D10" s="3">
-        <v>3171278132</v>
+        <v>4353562338</v>
       </c>
       <c r="E10" s="3">
-        <v>4723913148</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2898635098</v>
-      </c>
-      <c r="G10" s="3">
-        <v>4561101622</v>
-      </c>
-      <c r="H10" s="3">
-        <v>4561101622</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>295</v>
+        <v>3795489195</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
@@ -1646,16 +1559,16 @@
         <v>22</v>
       </c>
       <c r="B11" s="11">
-        <v>1506318334</v>
+        <v>1522019647</v>
       </c>
       <c r="C11" s="3">
-        <v>3190395207</v>
+        <v>3939765703</v>
       </c>
       <c r="D11" s="3">
-        <v>3135875161</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>294</v>
+        <v>3795487618</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
@@ -1663,31 +1576,28 @@
         <v>23</v>
       </c>
       <c r="B12" s="11">
-        <v>1506319032</v>
+        <v>1522022092</v>
       </c>
       <c r="C12" s="3">
-        <v>2963299035</v>
+        <v>4420199473</v>
       </c>
       <c r="D12" s="3">
-        <v>3171275438</v>
+        <v>4353528994</v>
       </c>
       <c r="E12" s="3">
-        <v>3130418484</v>
+        <v>3939764635</v>
       </c>
       <c r="F12" s="3">
-        <v>4723915575</v>
+        <v>3795489637</v>
       </c>
       <c r="G12" s="3">
-        <v>2898637313</v>
+        <v>3678859621</v>
       </c>
       <c r="H12" s="3">
-        <v>4561091202</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2873298950</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>294</v>
+        <v>4724084510</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -1695,34 +1605,19 @@
         <v>24</v>
       </c>
       <c r="B13" s="11">
-        <v>1506318356</v>
+        <v>1522019312</v>
       </c>
       <c r="C13" s="3">
-        <v>2871996198</v>
+        <v>4420199279</v>
       </c>
       <c r="D13" s="3">
-        <v>2963302353</v>
+        <v>4353528150</v>
       </c>
       <c r="E13" s="3">
-        <v>3171275249</v>
-      </c>
-      <c r="F13" s="3">
-        <v>3686480344</v>
-      </c>
-      <c r="G13" s="3">
-        <v>4723913134</v>
-      </c>
-      <c r="H13" s="3">
-        <v>2898638037</v>
-      </c>
-      <c r="I13" s="3">
-        <v>4561107516</v>
-      </c>
-      <c r="J13" s="3">
-        <v>2873298258</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>295</v>
+        <v>3795492355</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -1730,37 +1625,22 @@
         <v>25</v>
       </c>
       <c r="B14" s="11">
-        <v>1506319347</v>
+        <v>1522019474</v>
       </c>
       <c r="C14" s="3">
-        <v>2963301941</v>
+        <v>4362034147</v>
       </c>
       <c r="D14" s="3">
-        <v>2871997019</v>
+        <v>3795489923</v>
       </c>
       <c r="E14" s="3">
-        <v>3171275620</v>
+        <v>3939762692</v>
       </c>
       <c r="F14" s="3">
-        <v>3686479075</v>
-      </c>
-      <c r="G14" s="3">
-        <v>4723913286</v>
-      </c>
-      <c r="H14" s="3">
-        <v>2898635656</v>
-      </c>
-      <c r="I14" s="3">
-        <v>4445002255</v>
-      </c>
-      <c r="J14" s="3">
-        <v>4561106321</v>
-      </c>
-      <c r="K14" s="3">
-        <v>2873298548</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>295</v>
+        <v>4724088385</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
@@ -1768,16 +1648,25 @@
         <v>26</v>
       </c>
       <c r="B15" s="11">
-        <v>1506320185</v>
+        <v>1522020629</v>
       </c>
       <c r="C15" s="3">
-        <v>3939763279</v>
+        <v>4420198109</v>
       </c>
       <c r="D15" s="3">
-        <v>3795490035</v>
+        <v>4353561599</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3795491415</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3939765746</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3678856208</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -1785,13 +1674,16 @@
         <v>27</v>
       </c>
       <c r="B16" s="11">
-        <v>1506331467</v>
+        <v>1522020596</v>
       </c>
       <c r="C16" s="3">
-        <v>3678859195</v>
+        <v>4362037548</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3939765957</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
@@ -1799,34 +1691,19 @@
         <v>28</v>
       </c>
       <c r="B17" s="11">
-        <v>1506372679</v>
-      </c>
-      <c r="C17" s="5">
-        <v>2872000462</v>
+        <v>1522019498</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3795488393</v>
       </c>
       <c r="D17" s="3">
-        <v>2963301693</v>
+        <v>4362032491</v>
       </c>
       <c r="E17" s="3">
-        <v>3171276035</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3130413920</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4723913926</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2898636763</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4561091741</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2873299334</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>295</v>
+        <v>3939763800</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
@@ -1834,22 +1711,10 @@
         <v>29</v>
       </c>
       <c r="B18" s="11">
-        <v>1522021181</v>
-      </c>
-      <c r="C18" s="3">
-        <v>4420197936</v>
-      </c>
-      <c r="D18" s="3">
-        <v>4353534394</v>
-      </c>
-      <c r="E18" s="3">
-        <v>3939765424</v>
-      </c>
-      <c r="F18" s="3">
-        <v>3795491581</v>
+        <v>1522019450</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
@@ -1857,16 +1722,19 @@
         <v>30</v>
       </c>
       <c r="B19" s="11">
-        <v>1522019560</v>
+        <v>1522019276</v>
       </c>
       <c r="C19" s="3">
-        <v>3939760105</v>
+        <v>3795492821</v>
       </c>
       <c r="D19" s="3">
-        <v>3939760105</v>
+        <v>3939772595</v>
+      </c>
+      <c r="E19" s="3">
+        <v>4724083630</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
@@ -1874,22 +1742,22 @@
         <v>31</v>
       </c>
       <c r="B20" s="11">
-        <v>1522019577</v>
+        <v>1522019477</v>
       </c>
       <c r="C20" s="3">
-        <v>4353522509</v>
+        <v>4420197957</v>
       </c>
       <c r="D20" s="3">
-        <v>3795489493</v>
+        <v>4353542881</v>
       </c>
       <c r="E20" s="3">
-        <v>4420198417</v>
+        <v>3939765024</v>
       </c>
       <c r="F20" s="3">
-        <v>3678858448</v>
+        <v>4420198779</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -1897,16 +1765,16 @@
         <v>32</v>
       </c>
       <c r="B21" s="11">
-        <v>1522021741</v>
+        <v>1522019374</v>
       </c>
       <c r="C21" s="3">
-        <v>3795490630</v>
+        <v>3795489213</v>
       </c>
       <c r="D21" s="3">
-        <v>3939763988</v>
+        <v>3678857437</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
@@ -1914,19 +1782,25 @@
         <v>33</v>
       </c>
       <c r="B22" s="11">
-        <v>1522019667</v>
+        <v>1522020719</v>
       </c>
       <c r="C22" s="3">
-        <v>4420199383</v>
+        <v>3795492003</v>
       </c>
       <c r="D22" s="3">
-        <v>4353562338</v>
+        <v>4420198572</v>
       </c>
       <c r="E22" s="3">
-        <v>3795489195</v>
+        <v>4353583420</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3939767626</v>
+      </c>
+      <c r="G22" s="3">
+        <v>3678858225</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
@@ -1934,16 +1808,28 @@
         <v>34</v>
       </c>
       <c r="B23" s="11">
-        <v>1522019647</v>
-      </c>
-      <c r="C23" s="3">
-        <v>3939765703</v>
+        <v>1522021003</v>
+      </c>
+      <c r="C23" s="5">
+        <v>4420198568</v>
       </c>
       <c r="D23" s="3">
-        <v>3795487618</v>
+        <v>4353545450</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3795492116</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3939767405</v>
+      </c>
+      <c r="G23" s="3">
+        <v>3678858373</v>
+      </c>
+      <c r="H23" s="3">
+        <v>4724083351</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
@@ -1951,28 +1837,25 @@
         <v>35</v>
       </c>
       <c r="B24" s="11">
-        <v>1522022092</v>
+        <v>1522019733</v>
       </c>
       <c r="C24" s="3">
-        <v>4420199473</v>
+        <v>4420198644</v>
       </c>
       <c r="D24" s="3">
-        <v>4353528994</v>
+        <v>3795492977</v>
       </c>
       <c r="E24" s="3">
-        <v>3939764635</v>
+        <v>3939772038</v>
       </c>
       <c r="F24" s="3">
-        <v>3795489637</v>
+        <v>4353515818</v>
       </c>
       <c r="G24" s="3">
-        <v>3678859621</v>
-      </c>
-      <c r="H24" s="3">
-        <v>4724084510</v>
+        <v>3678868875</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
@@ -1980,19 +1863,25 @@
         <v>36</v>
       </c>
       <c r="B25" s="11">
-        <v>1522019312</v>
+        <v>1522019774</v>
       </c>
       <c r="C25" s="3">
-        <v>4420199279</v>
+        <v>4420198138</v>
       </c>
       <c r="D25" s="3">
-        <v>4353528150</v>
+        <v>4353559130</v>
       </c>
       <c r="E25" s="3">
-        <v>3795492355</v>
+        <v>3939775938</v>
+      </c>
+      <c r="F25" s="3">
+        <v>3795492421</v>
+      </c>
+      <c r="G25" s="3">
+        <v>3678869173</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
@@ -2000,22 +1889,28 @@
         <v>37</v>
       </c>
       <c r="B26" s="11">
-        <v>1522019474</v>
+        <v>1522020277</v>
       </c>
       <c r="C26" s="3">
-        <v>4362034147</v>
+        <v>4353538638</v>
       </c>
       <c r="D26" s="3">
-        <v>3795489923</v>
+        <v>3795492621</v>
       </c>
       <c r="E26" s="3">
-        <v>3939762692</v>
+        <v>3939766276</v>
       </c>
       <c r="F26" s="3">
-        <v>4724088385</v>
+        <v>4420198508</v>
+      </c>
+      <c r="G26" s="3">
+        <v>3678858866</v>
+      </c>
+      <c r="H26" s="3">
+        <v>4724083134</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
@@ -2023,25 +1918,25 @@
         <v>38</v>
       </c>
       <c r="B27" s="11">
-        <v>1522020629</v>
+        <v>1522021193</v>
       </c>
       <c r="C27" s="3">
-        <v>4420198109</v>
+        <v>4420198121</v>
       </c>
       <c r="D27" s="3">
-        <v>4353561599</v>
+        <v>4353522904</v>
       </c>
       <c r="E27" s="3">
-        <v>3795491415</v>
+        <v>3939773412</v>
       </c>
       <c r="F27" s="3">
-        <v>3939765746</v>
+        <v>3795489949</v>
       </c>
       <c r="G27" s="3">
-        <v>3678856208</v>
+        <v>3678867222</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
@@ -2049,16 +1944,28 @@
         <v>39</v>
       </c>
       <c r="B28" s="11">
-        <v>1522020596</v>
+        <v>1522020909</v>
       </c>
       <c r="C28" s="3">
-        <v>4362037548</v>
+        <v>4420198289</v>
       </c>
       <c r="D28" s="3">
-        <v>3939765957</v>
+        <v>4353570835</v>
+      </c>
+      <c r="E28" s="3">
+        <v>3795490714</v>
+      </c>
+      <c r="F28" s="3">
+        <v>3939767545</v>
+      </c>
+      <c r="G28" s="3">
+        <v>3678867791</v>
+      </c>
+      <c r="H28" s="3">
+        <v>4724084366</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
@@ -2066,19 +1973,19 @@
         <v>40</v>
       </c>
       <c r="B29" s="11">
-        <v>1522019498</v>
+        <v>1522019550</v>
       </c>
       <c r="C29" s="3">
-        <v>3795488393</v>
+        <v>4362032057</v>
       </c>
       <c r="D29" s="3">
-        <v>4362032491</v>
+        <v>3939761434</v>
       </c>
       <c r="E29" s="3">
-        <v>3939763800</v>
+        <v>3795489593</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
@@ -2086,10 +1993,31 @@
         <v>41</v>
       </c>
       <c r="B30" s="11">
-        <v>1522019450</v>
+        <v>1522019568</v>
+      </c>
+      <c r="C30" s="3">
+        <v>3795490882</v>
+      </c>
+      <c r="D30" s="3">
+        <v>4317330473</v>
+      </c>
+      <c r="E30" s="3">
+        <v>4725028406</v>
+      </c>
+      <c r="F30" s="3">
+        <v>4024288910</v>
+      </c>
+      <c r="G30" s="3">
+        <v>4730885327</v>
+      </c>
+      <c r="H30" s="3">
+        <v>3678857947</v>
+      </c>
+      <c r="I30" s="3">
+        <v>4513707779</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
@@ -2097,19 +2025,25 @@
         <v>42</v>
       </c>
       <c r="B31" s="11">
-        <v>1522019276</v>
+        <v>1522019564</v>
       </c>
       <c r="C31" s="3">
-        <v>3795492821</v>
+        <v>4420198106</v>
       </c>
       <c r="D31" s="3">
-        <v>3939772595</v>
+        <v>3795494638</v>
       </c>
       <c r="E31" s="3">
-        <v>4724083630</v>
+        <v>4353633095</v>
+      </c>
+      <c r="F31" s="3">
+        <v>3939767557</v>
+      </c>
+      <c r="G31" s="3">
+        <v>3678869285</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
@@ -2117,22 +2051,22 @@
         <v>43</v>
       </c>
       <c r="B32" s="11">
-        <v>1522019477</v>
+        <v>1522019743</v>
       </c>
       <c r="C32" s="3">
-        <v>4420197957</v>
+        <v>4420198354</v>
       </c>
       <c r="D32" s="3">
-        <v>4353542881</v>
+        <v>3939762996</v>
       </c>
       <c r="E32" s="3">
-        <v>3939765024</v>
+        <v>4353520181</v>
       </c>
       <c r="F32" s="3">
-        <v>4420198779</v>
+        <v>3795488259</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
@@ -2140,16 +2074,19 @@
         <v>44</v>
       </c>
       <c r="B33" s="11">
-        <v>1522019374</v>
+        <v>1522019636</v>
       </c>
       <c r="C33" s="3">
-        <v>3795489213</v>
+        <v>3795491539</v>
       </c>
       <c r="D33" s="3">
-        <v>3678857437</v>
+        <v>3939767253</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3678870845</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
@@ -2157,25 +2094,25 @@
         <v>45</v>
       </c>
       <c r="B34" s="11">
-        <v>1522020719</v>
+        <v>1522019666</v>
       </c>
       <c r="C34" s="3">
-        <v>3795492003</v>
+        <v>4353515787</v>
       </c>
       <c r="D34" s="3">
-        <v>4420198572</v>
+        <v>3939770576</v>
       </c>
       <c r="E34" s="3">
-        <v>4353583420</v>
+        <v>4420198334</v>
       </c>
       <c r="F34" s="3">
-        <v>3939767626</v>
+        <v>3795489344</v>
       </c>
       <c r="G34" s="3">
-        <v>3678858225</v>
+        <v>3678867757</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
@@ -2183,28 +2120,19 @@
         <v>46</v>
       </c>
       <c r="B35" s="11">
-        <v>1522021003</v>
-      </c>
-      <c r="C35" s="5">
-        <v>4420198568</v>
+        <v>1522019730</v>
+      </c>
+      <c r="C35" s="3">
+        <v>4362029972</v>
       </c>
       <c r="D35" s="3">
-        <v>4353545450</v>
+        <v>3939763530</v>
       </c>
       <c r="E35" s="3">
-        <v>3795492116</v>
-      </c>
-      <c r="F35" s="3">
-        <v>3939767405</v>
-      </c>
-      <c r="G35" s="3">
-        <v>3678858373</v>
-      </c>
-      <c r="H35" s="3">
-        <v>4724083351</v>
+        <v>3795491892</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
@@ -2212,25 +2140,19 @@
         <v>47</v>
       </c>
       <c r="B36" s="11">
-        <v>1522019733</v>
+        <v>1522019906</v>
       </c>
       <c r="C36" s="3">
-        <v>4420198644</v>
+        <v>4362030783</v>
       </c>
       <c r="D36" s="3">
-        <v>3795492977</v>
+        <v>3939769102</v>
       </c>
       <c r="E36" s="3">
-        <v>3939772038</v>
-      </c>
-      <c r="F36" s="3">
-        <v>4353515818</v>
-      </c>
-      <c r="G36" s="3">
-        <v>3678868875</v>
+        <v>3795491512</v>
       </c>
       <c r="P36" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
@@ -2238,25 +2160,13 @@
         <v>48</v>
       </c>
       <c r="B37" s="11">
-        <v>1522019774</v>
+        <v>1522020325</v>
       </c>
       <c r="C37" s="3">
-        <v>4420198138</v>
-      </c>
-      <c r="D37" s="3">
-        <v>4353559130</v>
-      </c>
-      <c r="E37" s="3">
-        <v>3939775938</v>
-      </c>
-      <c r="F37" s="3">
-        <v>3795492421</v>
-      </c>
-      <c r="G37" s="3">
-        <v>3678869173</v>
+        <v>3795489222</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
@@ -2264,28 +2174,19 @@
         <v>49</v>
       </c>
       <c r="B38" s="11">
-        <v>1522020277</v>
+        <v>1522019613</v>
       </c>
       <c r="C38" s="3">
-        <v>4353538638</v>
+        <v>4362036653</v>
       </c>
       <c r="D38" s="3">
-        <v>3795492621</v>
+        <v>3939763453</v>
       </c>
       <c r="E38" s="3">
-        <v>3939766276</v>
-      </c>
-      <c r="F38" s="3">
-        <v>4420198508</v>
-      </c>
-      <c r="G38" s="3">
-        <v>3678858866</v>
-      </c>
-      <c r="H38" s="3">
-        <v>4724083134</v>
+        <v>3678868658</v>
       </c>
       <c r="P38" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
@@ -2293,25 +2194,22 @@
         <v>50</v>
       </c>
       <c r="B39" s="11">
-        <v>1522021193</v>
+        <v>1522019292</v>
       </c>
       <c r="C39" s="3">
-        <v>4420198121</v>
+        <v>4420199328</v>
       </c>
       <c r="D39" s="3">
-        <v>4353522904</v>
+        <v>4353573356</v>
       </c>
       <c r="E39" s="3">
-        <v>3939773412</v>
+        <v>3795490081</v>
       </c>
       <c r="F39" s="3">
-        <v>3795489949</v>
-      </c>
-      <c r="G39" s="3">
-        <v>3678867222</v>
+        <v>3678859650</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
@@ -2319,28 +2217,19 @@
         <v>51</v>
       </c>
       <c r="B40" s="11">
-        <v>1522020909</v>
+        <v>1522020897</v>
       </c>
       <c r="C40" s="3">
-        <v>4420198289</v>
+        <v>3795491060</v>
       </c>
       <c r="D40" s="3">
-        <v>4353570835</v>
+        <v>3678859226</v>
       </c>
       <c r="E40" s="3">
-        <v>3795490714</v>
-      </c>
-      <c r="F40" s="3">
-        <v>3939767545</v>
-      </c>
-      <c r="G40" s="3">
-        <v>3678867791</v>
-      </c>
-      <c r="H40" s="3">
-        <v>4724084366</v>
+        <v>4724087690</v>
       </c>
       <c r="P40" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
@@ -2348,19 +2237,25 @@
         <v>52</v>
       </c>
       <c r="B41" s="11">
-        <v>1522019550</v>
+        <v>1522020059</v>
       </c>
       <c r="C41" s="3">
-        <v>4362032057</v>
+        <v>4420197436</v>
       </c>
       <c r="D41" s="3">
-        <v>3939761434</v>
+        <v>4353558250</v>
       </c>
       <c r="E41" s="3">
-        <v>3795489593</v>
+        <v>3795492186</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3939767518</v>
+      </c>
+      <c r="G41" s="3">
+        <v>4724084275</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
@@ -2368,31 +2263,22 @@
         <v>53</v>
       </c>
       <c r="B42" s="11">
-        <v>1522019568</v>
+        <v>1522020599</v>
       </c>
       <c r="C42" s="3">
-        <v>3795490882</v>
+        <v>4420198249</v>
       </c>
       <c r="D42" s="3">
-        <v>4317330473</v>
+        <v>4353647105</v>
       </c>
       <c r="E42" s="3">
-        <v>4725028406</v>
+        <v>3795493415</v>
       </c>
       <c r="F42" s="3">
-        <v>4024288910</v>
-      </c>
-      <c r="G42" s="3">
-        <v>4730885327</v>
-      </c>
-      <c r="H42" s="3">
-        <v>3678857947</v>
-      </c>
-      <c r="I42" s="3">
-        <v>4513707779</v>
+        <v>3678867391</v>
       </c>
       <c r="P42" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
@@ -2400,25 +2286,19 @@
         <v>54</v>
       </c>
       <c r="B43" s="11">
-        <v>1522019564</v>
+        <v>1522019725</v>
       </c>
       <c r="C43" s="3">
-        <v>4420198106</v>
+        <v>3795490784</v>
       </c>
       <c r="D43" s="3">
-        <v>3795494638</v>
+        <v>3939763736</v>
       </c>
       <c r="E43" s="3">
-        <v>4353633095</v>
-      </c>
-      <c r="F43" s="3">
-        <v>3939767557</v>
-      </c>
-      <c r="G43" s="3">
-        <v>3678869285</v>
+        <v>3678869127</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
@@ -2426,22 +2306,22 @@
         <v>55</v>
       </c>
       <c r="B44" s="11">
-        <v>1522019743</v>
+        <v>1522067175</v>
       </c>
       <c r="C44" s="3">
-        <v>4420198354</v>
+        <v>3795489760</v>
       </c>
       <c r="D44" s="3">
-        <v>3939762996</v>
+        <v>3939770997</v>
       </c>
       <c r="E44" s="3">
-        <v>4353520181</v>
+        <v>3678869113</v>
       </c>
       <c r="F44" s="3">
-        <v>3795488259</v>
+        <v>4724084231</v>
       </c>
       <c r="P44" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -2449,19 +2329,25 @@
         <v>56</v>
       </c>
       <c r="B45" s="11">
-        <v>1522019636</v>
+        <v>1532938950</v>
       </c>
       <c r="C45" s="3">
-        <v>3795491539</v>
+        <v>4420197310</v>
       </c>
       <c r="D45" s="3">
-        <v>3939767253</v>
+        <v>3939771041</v>
       </c>
       <c r="E45" s="3">
-        <v>3678870845</v>
+        <v>4353536011</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3795491649</v>
+      </c>
+      <c r="G45" s="3">
+        <v>3678860029</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -2469,25 +2355,16 @@
         <v>57</v>
       </c>
       <c r="B46" s="11">
-        <v>1522019666</v>
+        <v>1532937945</v>
       </c>
       <c r="C46" s="3">
-        <v>4353515787</v>
+        <v>3795492688</v>
       </c>
       <c r="D46" s="3">
-        <v>3939770576</v>
-      </c>
-      <c r="E46" s="3">
-        <v>4420198334</v>
-      </c>
-      <c r="F46" s="3">
-        <v>3795489344</v>
-      </c>
-      <c r="G46" s="3">
-        <v>3678867757</v>
+        <v>4753796086</v>
       </c>
       <c r="P46" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
@@ -2495,19 +2372,34 @@
         <v>58</v>
       </c>
       <c r="B47" s="11">
-        <v>1522019730</v>
+        <v>1532936652</v>
       </c>
       <c r="C47" s="3">
-        <v>4362029972</v>
+        <v>2872000090</v>
       </c>
       <c r="D47" s="3">
-        <v>3939763530</v>
+        <v>2963299371</v>
       </c>
       <c r="E47" s="3">
-        <v>3795491892</v>
-      </c>
-      <c r="P47" s="7" t="s">
-        <v>296</v>
+        <v>3171278729</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3130414680</v>
+      </c>
+      <c r="G47" s="3">
+        <v>4723915481</v>
+      </c>
+      <c r="H47" s="3">
+        <v>2898637440</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4561081632</v>
+      </c>
+      <c r="J47" s="3">
+        <v>2873304879</v>
+      </c>
+      <c r="P47" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
@@ -2515,19 +2407,22 @@
         <v>59</v>
       </c>
       <c r="B48" s="11">
-        <v>1522019906</v>
+        <v>1532938508</v>
       </c>
       <c r="C48" s="3">
-        <v>4362030783</v>
+        <v>3795491070</v>
       </c>
       <c r="D48" s="3">
-        <v>3939769102</v>
+        <v>4353544099</v>
       </c>
       <c r="E48" s="3">
-        <v>3795491512</v>
+        <v>4420199052</v>
+      </c>
+      <c r="F48" s="3">
+        <v>3939773240</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
@@ -2535,13 +2430,10 @@
         <v>60</v>
       </c>
       <c r="B49" s="11">
-        <v>1522020325</v>
-      </c>
-      <c r="C49" s="3">
-        <v>3795489222</v>
+        <v>1532940236</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
@@ -2549,19 +2441,25 @@
         <v>61</v>
       </c>
       <c r="B50" s="11">
-        <v>1522019613</v>
+        <v>1532938265</v>
       </c>
       <c r="C50" s="3">
-        <v>4362036653</v>
+        <v>4420198776</v>
       </c>
       <c r="D50" s="3">
-        <v>3939763453</v>
+        <v>4353636935</v>
       </c>
       <c r="E50" s="3">
-        <v>3678868658</v>
+        <v>3939767925</v>
+      </c>
+      <c r="F50" s="3">
+        <v>3795491534</v>
+      </c>
+      <c r="G50" s="3">
+        <v>3678867940</v>
       </c>
       <c r="P50" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
@@ -2569,22 +2467,31 @@
         <v>62</v>
       </c>
       <c r="B51" s="11">
-        <v>1522019292</v>
+        <v>1532938234</v>
       </c>
       <c r="C51" s="3">
-        <v>4420199328</v>
+        <v>2963300606</v>
       </c>
       <c r="D51" s="3">
-        <v>4353573356</v>
+        <v>3171277550</v>
       </c>
       <c r="E51" s="3">
-        <v>3795490081</v>
+        <v>3130417156</v>
       </c>
       <c r="F51" s="3">
-        <v>3678859650</v>
-      </c>
-      <c r="P51" s="7" t="s">
-        <v>296</v>
+        <v>4723918684</v>
+      </c>
+      <c r="G51" s="3">
+        <v>2898637568</v>
+      </c>
+      <c r="H51" s="3">
+        <v>4561090460</v>
+      </c>
+      <c r="I51" s="3">
+        <v>2873297756</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
@@ -2592,19 +2499,31 @@
         <v>63</v>
       </c>
       <c r="B52" s="11">
-        <v>1522020897</v>
+        <v>1532937049</v>
       </c>
       <c r="C52" s="3">
-        <v>3795491060</v>
+        <v>2963304021</v>
       </c>
       <c r="D52" s="3">
-        <v>3678859226</v>
+        <v>3171275519</v>
       </c>
       <c r="E52" s="3">
-        <v>4724087690</v>
-      </c>
-      <c r="P52" s="7" t="s">
-        <v>296</v>
+        <v>3130418125</v>
+      </c>
+      <c r="F52" s="3">
+        <v>4723915390</v>
+      </c>
+      <c r="G52" s="3">
+        <v>2898637974</v>
+      </c>
+      <c r="H52" s="3">
+        <v>4561095060</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2873298550</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
@@ -2612,25 +2531,31 @@
         <v>64</v>
       </c>
       <c r="B53" s="11">
-        <v>1522020059</v>
+        <v>1532937844</v>
       </c>
       <c r="C53" s="3">
-        <v>4420197436</v>
+        <v>2871997209</v>
       </c>
       <c r="D53" s="3">
-        <v>4353558250</v>
+        <v>2963303507</v>
       </c>
       <c r="E53" s="3">
-        <v>3795492186</v>
+        <v>3171275724</v>
       </c>
       <c r="F53" s="3">
-        <v>3939767518</v>
+        <v>4723915339</v>
       </c>
       <c r="G53" s="3">
-        <v>4724084275</v>
-      </c>
-      <c r="P53" s="7" t="s">
-        <v>296</v>
+        <v>2898635951</v>
+      </c>
+      <c r="H53" s="3">
+        <v>4561084915</v>
+      </c>
+      <c r="I53" s="3">
+        <v>2873298641</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
@@ -2638,22 +2563,10 @@
         <v>65</v>
       </c>
       <c r="B54" s="11">
-        <v>1522020599</v>
-      </c>
-      <c r="C54" s="3">
-        <v>4420198249</v>
-      </c>
-      <c r="D54" s="3">
-        <v>4353647105</v>
-      </c>
-      <c r="E54" s="3">
-        <v>3795493415</v>
-      </c>
-      <c r="F54" s="3">
-        <v>3678867391</v>
-      </c>
-      <c r="P54" s="7" t="s">
-        <v>296</v>
+        <v>1532936774</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
@@ -2661,19 +2574,34 @@
         <v>66</v>
       </c>
       <c r="B55" s="11">
-        <v>1522019725</v>
+        <v>1532936693</v>
       </c>
       <c r="C55" s="3">
-        <v>3795490784</v>
+        <v>2872000843</v>
       </c>
       <c r="D55" s="3">
-        <v>3939763736</v>
+        <v>2963300583</v>
       </c>
       <c r="E55" s="3">
-        <v>3678869127</v>
-      </c>
-      <c r="P55" s="7" t="s">
-        <v>296</v>
+        <v>3171275000</v>
+      </c>
+      <c r="F55" s="3">
+        <v>3130414604</v>
+      </c>
+      <c r="G55" s="3">
+        <v>4723916906</v>
+      </c>
+      <c r="H55" s="3">
+        <v>2898637076</v>
+      </c>
+      <c r="I55" s="3">
+        <v>4561078507</v>
+      </c>
+      <c r="J55" s="3">
+        <v>2873297833</v>
+      </c>
+      <c r="P55" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
@@ -2681,22 +2609,34 @@
         <v>67</v>
       </c>
       <c r="B56" s="11">
-        <v>1522067175</v>
+        <v>1533013698</v>
       </c>
       <c r="C56" s="3">
-        <v>3795489760</v>
+        <v>2963299835</v>
       </c>
       <c r="D56" s="3">
-        <v>3939770997</v>
+        <v>3171275638</v>
       </c>
       <c r="E56" s="3">
-        <v>3678869113</v>
+        <v>3130418459</v>
       </c>
       <c r="F56" s="3">
-        <v>4724084231</v>
-      </c>
-      <c r="P56" s="7" t="s">
-        <v>296</v>
+        <v>3686442346</v>
+      </c>
+      <c r="G56" s="3">
+        <v>4723916616</v>
+      </c>
+      <c r="H56" s="3">
+        <v>2898635695</v>
+      </c>
+      <c r="I56" s="3">
+        <v>4561093349</v>
+      </c>
+      <c r="J56" s="3">
+        <v>2873303946</v>
+      </c>
+      <c r="P56" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
@@ -2704,25 +2644,10 @@
         <v>68</v>
       </c>
       <c r="B57" s="11">
-        <v>1532938950</v>
-      </c>
-      <c r="C57" s="3">
-        <v>4420197310</v>
-      </c>
-      <c r="D57" s="3">
-        <v>3939771041</v>
-      </c>
-      <c r="E57" s="3">
-        <v>4353536011</v>
-      </c>
-      <c r="F57" s="3">
-        <v>3795491649</v>
-      </c>
-      <c r="G57" s="3">
-        <v>3678860029</v>
-      </c>
-      <c r="P57" s="7" t="s">
-        <v>296</v>
+        <v>1532937063</v>
+      </c>
+      <c r="P57" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
@@ -2730,16 +2655,10 @@
         <v>69</v>
       </c>
       <c r="B58" s="11">
-        <v>1532937945</v>
-      </c>
-      <c r="C58" s="3">
-        <v>3795492688</v>
-      </c>
-      <c r="D58" s="3">
-        <v>4753796086</v>
-      </c>
-      <c r="P58" s="7" t="s">
-        <v>296</v>
+        <v>1532937026</v>
+      </c>
+      <c r="P58" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
@@ -2747,34 +2666,10 @@
         <v>70</v>
       </c>
       <c r="B59" s="11">
-        <v>1532936652</v>
-      </c>
-      <c r="C59" s="3">
-        <v>2872000090</v>
-      </c>
-      <c r="D59" s="3">
-        <v>2963299371</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3171278729</v>
-      </c>
-      <c r="F59" s="3">
-        <v>3130414680</v>
-      </c>
-      <c r="G59" s="3">
-        <v>4723915481</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2898637440</v>
-      </c>
-      <c r="I59" s="3">
-        <v>4561081632</v>
-      </c>
-      <c r="J59" s="3">
-        <v>2873304879</v>
-      </c>
-      <c r="P59" s="8" t="s">
-        <v>295</v>
+        <v>1532940241</v>
+      </c>
+      <c r="P59" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
@@ -2782,22 +2677,16 @@
         <v>71</v>
       </c>
       <c r="B60" s="11">
-        <v>1532938508</v>
+        <v>1532960466</v>
       </c>
       <c r="C60" s="3">
-        <v>3795491070</v>
+        <v>2871996603</v>
       </c>
       <c r="D60" s="3">
-        <v>4353544099</v>
-      </c>
-      <c r="E60" s="3">
-        <v>4420199052</v>
-      </c>
-      <c r="F60" s="3">
-        <v>3939773240</v>
-      </c>
-      <c r="P60" s="7" t="s">
-        <v>296</v>
+        <v>4723915385</v>
+      </c>
+      <c r="P60" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
@@ -2805,10 +2694,40 @@
         <v>72</v>
       </c>
       <c r="B61" s="11">
-        <v>1532940236</v>
-      </c>
-      <c r="P61" s="7" t="s">
-        <v>296</v>
+        <v>1532937395</v>
+      </c>
+      <c r="C61" s="3">
+        <v>2871997054</v>
+      </c>
+      <c r="D61" s="3">
+        <v>2963299543</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2873298804</v>
+      </c>
+      <c r="F61" s="3">
+        <v>3171279276</v>
+      </c>
+      <c r="G61" s="3">
+        <v>3130414162</v>
+      </c>
+      <c r="H61" s="3">
+        <v>3686443955</v>
+      </c>
+      <c r="I61" s="3">
+        <v>4723916748</v>
+      </c>
+      <c r="J61" s="3">
+        <v>2898636170</v>
+      </c>
+      <c r="K61" s="3">
+        <v>4444949103</v>
+      </c>
+      <c r="L61" s="3">
+        <v>4561079268</v>
+      </c>
+      <c r="P61" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
@@ -2816,25 +2735,34 @@
         <v>73</v>
       </c>
       <c r="B62" s="11">
-        <v>1532938265</v>
+        <v>1532936207</v>
       </c>
       <c r="C62" s="3">
-        <v>4420198776</v>
+        <v>2871997797</v>
       </c>
       <c r="D62" s="3">
-        <v>4353636935</v>
+        <v>2963305475</v>
       </c>
       <c r="E62" s="3">
-        <v>3939767925</v>
+        <v>3171278743</v>
       </c>
       <c r="F62" s="3">
-        <v>3795491534</v>
+        <v>3130417699</v>
       </c>
       <c r="G62" s="3">
-        <v>3678867940</v>
-      </c>
-      <c r="P62" s="7" t="s">
-        <v>296</v>
+        <v>4723915144</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2898639712</v>
+      </c>
+      <c r="I62" s="3">
+        <v>4561083828</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2873299160</v>
+      </c>
+      <c r="P62" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
@@ -2842,31 +2770,19 @@
         <v>74</v>
       </c>
       <c r="B63" s="11">
-        <v>1532938234</v>
+        <v>1532938186</v>
       </c>
       <c r="C63" s="3">
-        <v>2963300606</v>
+        <v>3795492086</v>
       </c>
       <c r="D63" s="3">
-        <v>3171277550</v>
+        <v>4362035851</v>
       </c>
       <c r="E63" s="3">
-        <v>3130417156</v>
-      </c>
-      <c r="F63" s="3">
-        <v>4723918684</v>
-      </c>
-      <c r="G63" s="3">
-        <v>2898637568</v>
-      </c>
-      <c r="H63" s="3">
-        <v>4561090460</v>
-      </c>
-      <c r="I63" s="3">
-        <v>2873297756</v>
-      </c>
-      <c r="P63" s="6" t="s">
-        <v>294</v>
+        <v>3939765055</v>
+      </c>
+      <c r="P63" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.2">
@@ -2874,31 +2790,34 @@
         <v>75</v>
       </c>
       <c r="B64" s="11">
-        <v>1532937049</v>
+        <v>1532938464</v>
       </c>
       <c r="C64" s="3">
-        <v>2963304021</v>
+        <v>2963303452</v>
       </c>
       <c r="D64" s="3">
-        <v>3171275519</v>
+        <v>3171275602</v>
       </c>
       <c r="E64" s="3">
-        <v>3130418125</v>
+        <v>3130417489</v>
       </c>
       <c r="F64" s="3">
-        <v>4723915390</v>
+        <v>4723915911</v>
       </c>
       <c r="G64" s="3">
-        <v>2898637974</v>
+        <v>2898639561</v>
       </c>
       <c r="H64" s="3">
-        <v>4561095060</v>
+        <v>4444947765</v>
       </c>
       <c r="I64" s="3">
-        <v>2873298550</v>
+        <v>4561082127</v>
+      </c>
+      <c r="J64" s="3">
+        <v>2873298743</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
@@ -2906,31 +2825,19 @@
         <v>76</v>
       </c>
       <c r="B65" s="11">
-        <v>1532937844</v>
+        <v>1532939087</v>
       </c>
       <c r="C65" s="3">
-        <v>2871997209</v>
+        <v>3939767976</v>
       </c>
       <c r="D65" s="3">
-        <v>2963303507</v>
+        <v>3795487723</v>
       </c>
       <c r="E65" s="3">
-        <v>3171275724</v>
-      </c>
-      <c r="F65" s="3">
-        <v>4723915339</v>
-      </c>
-      <c r="G65" s="3">
-        <v>2898635951</v>
-      </c>
-      <c r="H65" s="3">
-        <v>4561084915</v>
-      </c>
-      <c r="I65" s="3">
-        <v>2873298641</v>
-      </c>
-      <c r="P65" s="6" t="s">
-        <v>294</v>
+        <v>4724084538</v>
+      </c>
+      <c r="P65" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.2">
@@ -2938,10 +2845,10 @@
         <v>77</v>
       </c>
       <c r="B66" s="11">
-        <v>1532936774</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>294</v>
+        <v>1532938438</v>
+      </c>
+      <c r="P66" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
@@ -2949,34 +2856,16 @@
         <v>78</v>
       </c>
       <c r="B67" s="11">
-        <v>1532936693</v>
+        <v>1532940015</v>
       </c>
       <c r="C67" s="3">
-        <v>2872000843</v>
+        <v>4362031470</v>
       </c>
       <c r="D67" s="3">
-        <v>2963300583</v>
-      </c>
-      <c r="E67" s="3">
-        <v>3171275000</v>
-      </c>
-      <c r="F67" s="3">
-        <v>3130414604</v>
-      </c>
-      <c r="G67" s="3">
-        <v>4723916906</v>
-      </c>
-      <c r="H67" s="3">
-        <v>2898637076</v>
-      </c>
-      <c r="I67" s="3">
-        <v>4561078507</v>
-      </c>
-      <c r="J67" s="3">
-        <v>2873297833</v>
-      </c>
-      <c r="P67" s="8" t="s">
-        <v>295</v>
+        <v>3939771934</v>
+      </c>
+      <c r="P67" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.2">
@@ -2984,34 +2873,19 @@
         <v>79</v>
       </c>
       <c r="B68" s="11">
-        <v>1533013698</v>
+        <v>1532939316</v>
       </c>
       <c r="C68" s="3">
-        <v>2963299835</v>
+        <v>4362030049</v>
       </c>
       <c r="D68" s="3">
-        <v>3171275638</v>
+        <v>3939771681</v>
       </c>
       <c r="E68" s="3">
-        <v>3130418459</v>
-      </c>
-      <c r="F68" s="3">
-        <v>3686442346</v>
-      </c>
-      <c r="G68" s="3">
-        <v>4723916616</v>
-      </c>
-      <c r="H68" s="3">
-        <v>2898635695</v>
-      </c>
-      <c r="I68" s="3">
-        <v>4561093349</v>
-      </c>
-      <c r="J68" s="3">
-        <v>2873303946</v>
-      </c>
-      <c r="P68" s="8" t="s">
-        <v>295</v>
+        <v>3795491665</v>
+      </c>
+      <c r="P68" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
@@ -3019,10 +2893,16 @@
         <v>80</v>
       </c>
       <c r="B69" s="11">
-        <v>1532937063</v>
-      </c>
-      <c r="P69" s="8" t="s">
-        <v>295</v>
+        <v>1532938476</v>
+      </c>
+      <c r="C69" s="3">
+        <v>3795491503</v>
+      </c>
+      <c r="D69" s="3">
+        <v>3939770708</v>
+      </c>
+      <c r="P69" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.2">
@@ -3030,10 +2910,34 @@
         <v>81</v>
       </c>
       <c r="B70" s="11">
-        <v>1532937026</v>
+        <v>1532938049</v>
+      </c>
+      <c r="C70" s="3">
+        <v>2871996669</v>
+      </c>
+      <c r="D70" s="3">
+        <v>2963302608</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3171276052</v>
+      </c>
+      <c r="F70" s="3">
+        <v>3686479171</v>
+      </c>
+      <c r="G70" s="3">
+        <v>4723912911</v>
+      </c>
+      <c r="H70" s="3">
+        <v>2898636910</v>
+      </c>
+      <c r="I70" s="3">
+        <v>4561112502</v>
+      </c>
+      <c r="J70" s="3">
+        <v>2873298244</v>
       </c>
       <c r="P70" s="8" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
@@ -3041,10 +2945,25 @@
         <v>82</v>
       </c>
       <c r="B71" s="11">
-        <v>1532940241</v>
+        <v>1532938204</v>
+      </c>
+      <c r="C71" s="3">
+        <v>4420198566</v>
+      </c>
+      <c r="D71" s="3">
+        <v>4353577415</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3939767078</v>
+      </c>
+      <c r="F71" s="3">
+        <v>3795492049</v>
+      </c>
+      <c r="G71" s="3">
+        <v>4724084174</v>
       </c>
       <c r="P71" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
@@ -3052,16 +2971,34 @@
         <v>83</v>
       </c>
       <c r="B72" s="11">
-        <v>1532960466</v>
+        <v>1532937525</v>
       </c>
       <c r="C72" s="3">
-        <v>2871996603</v>
+        <v>2871998241</v>
       </c>
       <c r="D72" s="3">
-        <v>4723915385</v>
-      </c>
-      <c r="P72" s="8" t="s">
-        <v>295</v>
+        <v>3171276199</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3130417756</v>
+      </c>
+      <c r="F72" s="3">
+        <v>4723915162</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2898646711</v>
+      </c>
+      <c r="H72" s="3">
+        <v>4444945210</v>
+      </c>
+      <c r="I72" s="3">
+        <v>4561091994</v>
+      </c>
+      <c r="J72" s="3">
+        <v>2873298342</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.2">
@@ -3069,40 +3006,10 @@
         <v>84</v>
       </c>
       <c r="B73" s="11">
-        <v>1532937395</v>
-      </c>
-      <c r="C73" s="3">
-        <v>2871997054</v>
-      </c>
-      <c r="D73" s="3">
-        <v>2963299543</v>
-      </c>
-      <c r="E73" s="3">
-        <v>2873298804</v>
-      </c>
-      <c r="F73" s="3">
-        <v>3171279276</v>
-      </c>
-      <c r="G73" s="3">
-        <v>3130414162</v>
-      </c>
-      <c r="H73" s="3">
-        <v>3686443955</v>
-      </c>
-      <c r="I73" s="3">
-        <v>4723916748</v>
-      </c>
-      <c r="J73" s="3">
-        <v>2898636170</v>
-      </c>
-      <c r="K73" s="3">
-        <v>4444949103</v>
-      </c>
-      <c r="L73" s="3">
-        <v>4561079268</v>
-      </c>
-      <c r="P73" s="8" t="s">
-        <v>295</v>
+        <v>1532938598</v>
+      </c>
+      <c r="P73" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.2">
@@ -3110,34 +3017,10 @@
         <v>85</v>
       </c>
       <c r="B74" s="11">
-        <v>1532936207</v>
-      </c>
-      <c r="C74" s="3">
-        <v>2871997797</v>
-      </c>
-      <c r="D74" s="3">
-        <v>2963305475</v>
-      </c>
-      <c r="E74" s="3">
-        <v>3171278743</v>
-      </c>
-      <c r="F74" s="3">
-        <v>3130417699</v>
-      </c>
-      <c r="G74" s="3">
-        <v>4723915144</v>
-      </c>
-      <c r="H74" s="3">
-        <v>2898639712</v>
-      </c>
-      <c r="I74" s="3">
-        <v>4561083828</v>
-      </c>
-      <c r="J74" s="3">
-        <v>2873299160</v>
+        <v>1532936617</v>
       </c>
       <c r="P74" s="8" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.2">
@@ -3145,19 +3028,34 @@
         <v>86</v>
       </c>
       <c r="B75" s="11">
-        <v>1532938186</v>
+        <v>1532939681</v>
       </c>
       <c r="C75" s="3">
-        <v>3795492086</v>
+        <v>4445933040</v>
       </c>
       <c r="D75" s="3">
-        <v>4362035851</v>
+        <v>4445936205</v>
       </c>
       <c r="E75" s="3">
-        <v>3939765055</v>
+        <v>3795460687</v>
+      </c>
+      <c r="F75" s="3">
+        <v>4155959554</v>
+      </c>
+      <c r="G75" s="3">
+        <v>3941707771</v>
+      </c>
+      <c r="H75" s="3">
+        <v>4752029779</v>
+      </c>
+      <c r="I75" s="3">
+        <v>4158565901</v>
+      </c>
+      <c r="J75" s="3">
+        <v>4466038283</v>
       </c>
       <c r="P75" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.2">
@@ -3165,34 +3063,10 @@
         <v>87</v>
       </c>
       <c r="B76" s="11">
-        <v>1532938464</v>
-      </c>
-      <c r="C76" s="3">
-        <v>2963303452</v>
-      </c>
-      <c r="D76" s="3">
-        <v>3171275602</v>
-      </c>
-      <c r="E76" s="3">
-        <v>3130417489</v>
-      </c>
-      <c r="F76" s="3">
-        <v>4723915911</v>
-      </c>
-      <c r="G76" s="3">
-        <v>2898639561</v>
-      </c>
-      <c r="H76" s="3">
-        <v>4444947765</v>
-      </c>
-      <c r="I76" s="3">
-        <v>4561082127</v>
-      </c>
-      <c r="J76" s="3">
-        <v>2873298743</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>294</v>
+        <v>1532936541</v>
+      </c>
+      <c r="P76" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.2">
@@ -3200,19 +3074,10 @@
         <v>88</v>
       </c>
       <c r="B77" s="11">
-        <v>1532939087</v>
-      </c>
-      <c r="C77" s="3">
-        <v>3939767976</v>
-      </c>
-      <c r="D77" s="3">
-        <v>3795487723</v>
-      </c>
-      <c r="E77" s="3">
-        <v>4724084538</v>
-      </c>
-      <c r="P77" s="7" t="s">
-        <v>296</v>
+        <v>1532936901</v>
+      </c>
+      <c r="P77" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.2">
@@ -3220,10 +3085,34 @@
         <v>89</v>
       </c>
       <c r="B78" s="11">
-        <v>1532938438</v>
+        <v>1532938459</v>
+      </c>
+      <c r="C78" s="3">
+        <v>4445959442</v>
+      </c>
+      <c r="D78" s="3">
+        <v>4445942617</v>
+      </c>
+      <c r="E78" s="3">
+        <v>4155959566</v>
+      </c>
+      <c r="F78" s="3">
+        <v>3795461038</v>
+      </c>
+      <c r="G78" s="3">
+        <v>3941780986</v>
+      </c>
+      <c r="H78" s="3">
+        <v>4752030743</v>
+      </c>
+      <c r="I78" s="3">
+        <v>4158566095</v>
+      </c>
+      <c r="J78" s="3">
+        <v>4466037381</v>
       </c>
       <c r="P78" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.2">
@@ -3231,16 +3120,34 @@
         <v>90</v>
       </c>
       <c r="B79" s="11">
-        <v>1532940015</v>
+        <v>1532936711</v>
       </c>
       <c r="C79" s="3">
-        <v>4362031470</v>
+        <v>2871996623</v>
       </c>
       <c r="D79" s="3">
-        <v>3939771934</v>
-      </c>
-      <c r="P79" s="7" t="s">
-        <v>296</v>
+        <v>2963298429</v>
+      </c>
+      <c r="E79" s="3">
+        <v>3171275736</v>
+      </c>
+      <c r="F79" s="3">
+        <v>3130414732</v>
+      </c>
+      <c r="G79" s="3">
+        <v>4723915979</v>
+      </c>
+      <c r="H79" s="3">
+        <v>2898645401</v>
+      </c>
+      <c r="I79" s="3">
+        <v>4561089831</v>
+      </c>
+      <c r="J79" s="3">
+        <v>2873298992</v>
+      </c>
+      <c r="P79" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.2">
@@ -3248,19 +3155,31 @@
         <v>91</v>
       </c>
       <c r="B80" s="11">
-        <v>1532939316</v>
+        <v>1532937018</v>
       </c>
       <c r="C80" s="3">
-        <v>4362030049</v>
+        <v>2963306192</v>
       </c>
       <c r="D80" s="3">
-        <v>3939771681</v>
+        <v>3171275017</v>
       </c>
       <c r="E80" s="3">
-        <v>3795491665</v>
-      </c>
-      <c r="P80" s="7" t="s">
-        <v>296</v>
+        <v>3130417686</v>
+      </c>
+      <c r="F80" s="3">
+        <v>4723915081</v>
+      </c>
+      <c r="G80" s="3">
+        <v>2898635907</v>
+      </c>
+      <c r="H80" s="3">
+        <v>4561093123</v>
+      </c>
+      <c r="I80" s="3">
+        <v>2873298693</v>
+      </c>
+      <c r="P80" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
@@ -3268,16 +3187,16 @@
         <v>92</v>
       </c>
       <c r="B81" s="11">
-        <v>1532938476</v>
+        <v>1532937318</v>
       </c>
       <c r="C81" s="3">
-        <v>3795491503</v>
+        <v>2871998257</v>
       </c>
       <c r="D81" s="3">
-        <v>3939770708</v>
-      </c>
-      <c r="P81" s="7" t="s">
-        <v>296</v>
+        <v>4723912898</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.2">
@@ -3285,34 +3204,16 @@
         <v>93</v>
       </c>
       <c r="B82" s="11">
-        <v>1532938049</v>
+        <v>1532967644</v>
       </c>
       <c r="C82" s="3">
-        <v>2871996669</v>
+        <v>4723911434</v>
       </c>
       <c r="D82" s="3">
-        <v>2963302608</v>
-      </c>
-      <c r="E82" s="3">
-        <v>3171276052</v>
-      </c>
-      <c r="F82" s="3">
-        <v>3686479171</v>
-      </c>
-      <c r="G82" s="3">
-        <v>4723912911</v>
-      </c>
-      <c r="H82" s="3">
-        <v>2898636910</v>
-      </c>
-      <c r="I82" s="3">
-        <v>4561112502</v>
-      </c>
-      <c r="J82" s="3">
-        <v>2873298244</v>
-      </c>
-      <c r="P82" s="8" t="s">
-        <v>295</v>
+        <v>4561099873</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
@@ -3320,25 +3221,34 @@
         <v>94</v>
       </c>
       <c r="B83" s="11">
-        <v>1532938204</v>
+        <v>1532967942</v>
       </c>
       <c r="C83" s="3">
-        <v>4420198566</v>
+        <v>2871998283</v>
       </c>
       <c r="D83" s="3">
-        <v>4353577415</v>
+        <v>2963300883</v>
       </c>
       <c r="E83" s="3">
-        <v>3939767078</v>
+        <v>3171278315</v>
       </c>
       <c r="F83" s="3">
-        <v>3795492049</v>
+        <v>3686479188</v>
       </c>
       <c r="G83" s="3">
-        <v>4724084174</v>
-      </c>
-      <c r="P83" s="7" t="s">
-        <v>296</v>
+        <v>4723913022</v>
+      </c>
+      <c r="H83" s="3">
+        <v>2898639858</v>
+      </c>
+      <c r="I83" s="3">
+        <v>4561102636</v>
+      </c>
+      <c r="J83" s="3">
+        <v>2873298500</v>
+      </c>
+      <c r="P83" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.2">
@@ -3346,34 +3256,34 @@
         <v>95</v>
       </c>
       <c r="B84" s="11">
-        <v>1532937525</v>
+        <v>1532966987</v>
       </c>
       <c r="C84" s="3">
-        <v>2871998241</v>
+        <v>2872001457</v>
       </c>
       <c r="D84" s="3">
-        <v>3171276199</v>
+        <v>2963301451</v>
       </c>
       <c r="E84" s="3">
-        <v>3130417756</v>
+        <v>3171275964</v>
       </c>
       <c r="F84" s="3">
-        <v>4723915162</v>
+        <v>3686477084</v>
       </c>
       <c r="G84" s="3">
-        <v>2898646711</v>
+        <v>4723913703</v>
       </c>
       <c r="H84" s="3">
-        <v>4444945210</v>
+        <v>2898637819</v>
       </c>
       <c r="I84" s="3">
-        <v>4561091994</v>
+        <v>4561101578</v>
       </c>
       <c r="J84" s="3">
-        <v>2873298342</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>294</v>
+        <v>2873298834</v>
+      </c>
+      <c r="P84" s="8" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.2">
@@ -3381,10 +3291,37 @@
         <v>96</v>
       </c>
       <c r="B85" s="11">
-        <v>1532938598</v>
-      </c>
-      <c r="P85" s="7" t="s">
-        <v>296</v>
+        <v>1532979233</v>
+      </c>
+      <c r="C85" s="3">
+        <v>2871996447</v>
+      </c>
+      <c r="D85" s="3">
+        <v>2963305959</v>
+      </c>
+      <c r="E85" s="3">
+        <v>3171275827</v>
+      </c>
+      <c r="F85" s="3">
+        <v>3130418146</v>
+      </c>
+      <c r="G85" s="3">
+        <v>4723916301</v>
+      </c>
+      <c r="H85" s="3">
+        <v>2898639884</v>
+      </c>
+      <c r="I85" s="3">
+        <v>4444964120</v>
+      </c>
+      <c r="J85" s="3">
+        <v>4561086317</v>
+      </c>
+      <c r="K85" s="3">
+        <v>2873306046</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.2">
@@ -3392,10 +3329,25 @@
         <v>97</v>
       </c>
       <c r="B86" s="11">
-        <v>1532936617</v>
-      </c>
-      <c r="P86" s="8" t="s">
-        <v>295</v>
+        <v>1563382131</v>
+      </c>
+      <c r="C86" s="3">
+        <v>4353328915</v>
+      </c>
+      <c r="D86" s="3">
+        <v>2585333507</v>
+      </c>
+      <c r="E86" s="3">
+        <v>3189693166</v>
+      </c>
+      <c r="F86" s="3">
+        <v>3192428174</v>
+      </c>
+      <c r="G86" s="3">
+        <v>3116751442</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.2">
@@ -3403,34 +3355,43 @@
         <v>98</v>
       </c>
       <c r="B87" s="11">
-        <v>1532939681</v>
+        <v>1563383242</v>
       </c>
       <c r="C87" s="3">
-        <v>4445933040</v>
+        <v>4445961876</v>
       </c>
       <c r="D87" s="3">
-        <v>4445936205</v>
+        <v>4445951582</v>
       </c>
       <c r="E87" s="3">
-        <v>3795460687</v>
+        <v>4752032039</v>
       </c>
       <c r="F87" s="3">
-        <v>4155959554</v>
+        <v>4155957965</v>
       </c>
       <c r="G87" s="3">
-        <v>3941707771</v>
+        <v>4158568605</v>
       </c>
       <c r="H87" s="3">
-        <v>4752029779</v>
+        <v>3795463132</v>
       </c>
       <c r="I87" s="3">
-        <v>4158565901</v>
+        <v>2585327771</v>
       </c>
       <c r="J87" s="3">
-        <v>4466038283</v>
-      </c>
-      <c r="P87" s="7" t="s">
-        <v>296</v>
+        <v>3189693819</v>
+      </c>
+      <c r="K87" s="3">
+        <v>3192428864</v>
+      </c>
+      <c r="L87" s="3">
+        <v>3116752250</v>
+      </c>
+      <c r="M87" s="3">
+        <v>4530261632</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.2">
@@ -3438,10 +3399,40 @@
         <v>99</v>
       </c>
       <c r="B88" s="11">
-        <v>1532936541</v>
-      </c>
-      <c r="P88" s="8" t="s">
-        <v>295</v>
+        <v>1563383107</v>
+      </c>
+      <c r="C88" s="3">
+        <v>4445941484</v>
+      </c>
+      <c r="D88" s="3">
+        <v>4445940255</v>
+      </c>
+      <c r="E88" s="3">
+        <v>4752033281</v>
+      </c>
+      <c r="F88" s="3">
+        <v>4155959263</v>
+      </c>
+      <c r="G88" s="3">
+        <v>4158567287</v>
+      </c>
+      <c r="H88" s="3">
+        <v>3795459702</v>
+      </c>
+      <c r="I88" s="3">
+        <v>2585325543</v>
+      </c>
+      <c r="J88" s="3">
+        <v>3192429221</v>
+      </c>
+      <c r="K88" s="3">
+        <v>3116751243</v>
+      </c>
+      <c r="L88" s="3">
+        <v>4530260427</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.2">
@@ -3449,10 +3440,43 @@
         <v>100</v>
       </c>
       <c r="B89" s="11">
-        <v>1532936901</v>
-      </c>
-      <c r="P89" s="8" t="s">
-        <v>295</v>
+        <v>1563383294</v>
+      </c>
+      <c r="C89" s="3">
+        <v>4445938219</v>
+      </c>
+      <c r="D89" s="3">
+        <v>4445942034</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4752034091</v>
+      </c>
+      <c r="F89" s="3">
+        <v>4158566592</v>
+      </c>
+      <c r="G89" s="3">
+        <v>4155960235</v>
+      </c>
+      <c r="H89" s="3">
+        <v>3795459019</v>
+      </c>
+      <c r="I89" s="3">
+        <v>3189692700</v>
+      </c>
+      <c r="J89" s="3">
+        <v>3192427748</v>
+      </c>
+      <c r="K89" s="3">
+        <v>2585328859</v>
+      </c>
+      <c r="L89" s="3">
+        <v>3116747411</v>
+      </c>
+      <c r="M89" s="3">
+        <v>4530263860</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.2">
@@ -3460,34 +3484,34 @@
         <v>101</v>
       </c>
       <c r="B90" s="11">
-        <v>1532938459</v>
+        <v>1625046334</v>
       </c>
       <c r="C90" s="3">
-        <v>4445959442</v>
+        <v>4445950675</v>
       </c>
       <c r="D90" s="3">
-        <v>4445942617</v>
+        <v>4445941119</v>
       </c>
       <c r="E90" s="3">
-        <v>4155959566</v>
+        <v>4155958279</v>
       </c>
       <c r="F90" s="3">
-        <v>3795461038</v>
+        <v>3941709950</v>
       </c>
       <c r="G90" s="3">
-        <v>3941780986</v>
+        <v>3795459634</v>
       </c>
       <c r="H90" s="3">
-        <v>4752030743</v>
+        <v>4752030098</v>
       </c>
       <c r="I90" s="3">
-        <v>4158566095</v>
+        <v>4158566136</v>
       </c>
       <c r="J90" s="3">
-        <v>4466037381</v>
+        <v>4466037745</v>
       </c>
       <c r="P90" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
@@ -3495,34 +3519,31 @@
         <v>102</v>
       </c>
       <c r="B91" s="11">
-        <v>1532936711</v>
+        <v>1625046271</v>
       </c>
       <c r="C91" s="3">
-        <v>2871996623</v>
+        <v>4445958574</v>
       </c>
       <c r="D91" s="3">
-        <v>2963298429</v>
+        <v>4445942120</v>
       </c>
       <c r="E91" s="3">
-        <v>3171275736</v>
+        <v>4752032489</v>
       </c>
       <c r="F91" s="3">
-        <v>3130414732</v>
+        <v>4158565875</v>
       </c>
       <c r="G91" s="3">
-        <v>4723915979</v>
+        <v>4155957041</v>
       </c>
       <c r="H91" s="3">
-        <v>2898645401</v>
+        <v>3795462734</v>
       </c>
       <c r="I91" s="3">
-        <v>4561089831</v>
-      </c>
-      <c r="J91" s="3">
-        <v>2873298992</v>
-      </c>
-      <c r="P91" s="8" t="s">
-        <v>295</v>
+        <v>4466038409</v>
+      </c>
+      <c r="P91" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.2">
@@ -3530,31 +3551,40 @@
         <v>103</v>
       </c>
       <c r="B92" s="11">
-        <v>1532937018</v>
+        <v>1625046227</v>
       </c>
       <c r="C92" s="3">
-        <v>2963306192</v>
+        <v>4445932577</v>
       </c>
       <c r="D92" s="3">
-        <v>3171275017</v>
+        <v>4445943218</v>
       </c>
       <c r="E92" s="3">
-        <v>3130417686</v>
+        <v>3795461973</v>
       </c>
       <c r="F92" s="3">
-        <v>4723915081</v>
+        <v>3863596639</v>
       </c>
       <c r="G92" s="3">
-        <v>2898635907</v>
+        <v>3941704155</v>
       </c>
       <c r="H92" s="3">
-        <v>4561093123</v>
+        <v>4023852927</v>
       </c>
       <c r="I92" s="3">
-        <v>2873298693</v>
-      </c>
-      <c r="P92" s="8" t="s">
-        <v>295</v>
+        <v>4752031588</v>
+      </c>
+      <c r="J92" s="3">
+        <v>4158567200</v>
+      </c>
+      <c r="K92" s="3">
+        <v>4155960192</v>
+      </c>
+      <c r="L92" s="3">
+        <v>4466036877</v>
+      </c>
+      <c r="P92" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.2">
@@ -3562,16 +3592,19 @@
         <v>104</v>
       </c>
       <c r="B93" s="11">
-        <v>1532937318</v>
+        <v>1625046247</v>
       </c>
       <c r="C93" s="3">
-        <v>2871998257</v>
+        <v>3941704334</v>
       </c>
       <c r="D93" s="3">
-        <v>4723912898</v>
-      </c>
-      <c r="P93" s="6" t="s">
-        <v>294</v>
+        <v>4353363603</v>
+      </c>
+      <c r="E93" s="3">
+        <v>4466038208</v>
+      </c>
+      <c r="P93" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.2">
@@ -3579,16 +3612,34 @@
         <v>105</v>
       </c>
       <c r="B94" s="11">
-        <v>1532967644</v>
+        <v>1625046385</v>
       </c>
       <c r="C94" s="3">
-        <v>4723911434</v>
+        <v>4445936896</v>
       </c>
       <c r="D94" s="3">
-        <v>4561099873</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>294</v>
+        <v>4445946886</v>
+      </c>
+      <c r="E94" s="3">
+        <v>3795460892</v>
+      </c>
+      <c r="F94" s="3">
+        <v>4155957539</v>
+      </c>
+      <c r="G94" s="3">
+        <v>3941704822</v>
+      </c>
+      <c r="H94" s="3">
+        <v>4752029020</v>
+      </c>
+      <c r="I94" s="3">
+        <v>4158565627</v>
+      </c>
+      <c r="J94" s="3">
+        <v>4466035346</v>
+      </c>
+      <c r="P94" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.2">
@@ -3596,34 +3647,31 @@
         <v>106</v>
       </c>
       <c r="B95" s="11">
-        <v>1532967942</v>
+        <v>1625046276</v>
       </c>
       <c r="C95" s="3">
-        <v>2871998283</v>
+        <v>4445948495</v>
       </c>
       <c r="D95" s="3">
-        <v>2963300883</v>
+        <v>4445956474</v>
       </c>
       <c r="E95" s="3">
-        <v>3171278315</v>
+        <v>3795461021</v>
       </c>
       <c r="F95" s="3">
-        <v>3686479188</v>
+        <v>4752030559</v>
       </c>
       <c r="G95" s="3">
-        <v>4723913022</v>
+        <v>4158567951</v>
       </c>
       <c r="H95" s="3">
-        <v>2898639858</v>
+        <v>4155958011</v>
       </c>
       <c r="I95" s="3">
-        <v>4561102636</v>
-      </c>
-      <c r="J95" s="3">
-        <v>2873298500</v>
-      </c>
-      <c r="P95" s="8" t="s">
-        <v>295</v>
+        <v>4466037689</v>
+      </c>
+      <c r="P95" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.2">
@@ -3631,34 +3679,34 @@
         <v>107</v>
       </c>
       <c r="B96" s="11">
-        <v>1532966987</v>
+        <v>1625046309</v>
       </c>
       <c r="C96" s="3">
-        <v>2872001457</v>
+        <v>4445953866</v>
       </c>
       <c r="D96" s="3">
-        <v>2963301451</v>
+        <v>4445944622</v>
       </c>
       <c r="E96" s="3">
-        <v>3171275964</v>
+        <v>3795461754</v>
       </c>
       <c r="F96" s="3">
-        <v>3686477084</v>
+        <v>4155959060</v>
       </c>
       <c r="G96" s="3">
-        <v>4723913703</v>
+        <v>3941714329</v>
       </c>
       <c r="H96" s="3">
-        <v>2898637819</v>
+        <v>4752027970</v>
       </c>
       <c r="I96" s="3">
-        <v>4561101578</v>
+        <v>4158567627</v>
       </c>
       <c r="J96" s="3">
-        <v>2873298834</v>
-      </c>
-      <c r="P96" s="8" t="s">
-        <v>295</v>
+        <v>4466038522</v>
+      </c>
+      <c r="P96" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.2">
@@ -3666,37 +3714,49 @@
         <v>108</v>
       </c>
       <c r="B97" s="11">
-        <v>1532979233</v>
+        <v>1625431183</v>
       </c>
       <c r="C97" s="3">
-        <v>2871996447</v>
+        <v>4445939379</v>
       </c>
       <c r="D97" s="3">
-        <v>2963305959</v>
+        <v>4445944074</v>
       </c>
       <c r="E97" s="3">
-        <v>3171275827</v>
+        <v>3795460373</v>
       </c>
       <c r="F97" s="3">
-        <v>3130418146</v>
+        <v>4752029752</v>
       </c>
       <c r="G97" s="3">
-        <v>4723916301</v>
+        <v>4158565677</v>
       </c>
       <c r="H97" s="3">
-        <v>2898639884</v>
+        <v>4155959485</v>
       </c>
       <c r="I97" s="3">
-        <v>4444964120</v>
+        <v>4538028555</v>
       </c>
       <c r="J97" s="3">
-        <v>4561086317</v>
+        <v>4661815305</v>
       </c>
       <c r="K97" s="3">
-        <v>2873306046</v>
-      </c>
-      <c r="P97" s="6" t="s">
-        <v>294</v>
+        <v>4529511202</v>
+      </c>
+      <c r="L97" s="3">
+        <v>4600377356</v>
+      </c>
+      <c r="M97" s="3">
+        <v>4691614999</v>
+      </c>
+      <c r="N97" s="3">
+        <v>4413868976</v>
+      </c>
+      <c r="O97" s="3">
+        <v>4466043329</v>
+      </c>
+      <c r="P97" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.2">
@@ -3704,25 +3764,16 @@
         <v>109</v>
       </c>
       <c r="B98" s="11">
-        <v>1563382131</v>
+        <v>1625431121</v>
       </c>
       <c r="C98" s="3">
-        <v>4353328915</v>
+        <v>4752031641</v>
       </c>
       <c r="D98" s="3">
-        <v>2585333507</v>
-      </c>
-      <c r="E98" s="3">
-        <v>3189693166</v>
-      </c>
-      <c r="F98" s="3">
-        <v>3192428174</v>
-      </c>
-      <c r="G98" s="3">
-        <v>3116751442</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>294</v>
+        <v>4466037450</v>
+      </c>
+      <c r="P98" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.2">
@@ -3730,43 +3781,34 @@
         <v>110</v>
       </c>
       <c r="B99" s="11">
-        <v>1563383242</v>
+        <v>1625431048</v>
       </c>
       <c r="C99" s="3">
-        <v>4445961876</v>
+        <v>4445946589</v>
       </c>
       <c r="D99" s="3">
-        <v>4445951582</v>
+        <v>4445943627</v>
       </c>
       <c r="E99" s="3">
-        <v>4752032039</v>
+        <v>3795461182</v>
       </c>
       <c r="F99" s="3">
-        <v>4155957965</v>
+        <v>3941713769</v>
       </c>
       <c r="G99" s="3">
-        <v>4158568605</v>
+        <v>4752032880</v>
       </c>
       <c r="H99" s="3">
-        <v>3795463132</v>
+        <v>4158566145</v>
       </c>
       <c r="I99" s="3">
-        <v>2585327771</v>
+        <v>4155958972</v>
       </c>
       <c r="J99" s="3">
-        <v>3189693819</v>
-      </c>
-      <c r="K99" s="3">
-        <v>3192428864</v>
-      </c>
-      <c r="L99" s="3">
-        <v>3116752250</v>
-      </c>
-      <c r="M99" s="3">
-        <v>4530261632</v>
-      </c>
-      <c r="P99" s="6" t="s">
-        <v>294</v>
+        <v>4466038473</v>
+      </c>
+      <c r="P99" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.2">
@@ -3774,40 +3816,34 @@
         <v>111</v>
       </c>
       <c r="B100" s="11">
-        <v>1563383107</v>
+        <v>1626838878</v>
       </c>
       <c r="C100" s="3">
-        <v>4445941484</v>
+        <v>4445947304</v>
       </c>
       <c r="D100" s="3">
-        <v>4445940255</v>
+        <v>4445950814</v>
       </c>
       <c r="E100" s="3">
-        <v>4752033281</v>
+        <v>4155958014</v>
       </c>
       <c r="F100" s="3">
-        <v>4155959263</v>
+        <v>3795464340</v>
       </c>
       <c r="G100" s="3">
-        <v>4158567287</v>
+        <v>4752030425</v>
       </c>
       <c r="H100" s="3">
-        <v>3795459702</v>
+        <v>4158568732</v>
       </c>
       <c r="I100" s="3">
-        <v>2585325543</v>
+        <v>4411164783</v>
       </c>
       <c r="J100" s="3">
-        <v>3192429221</v>
-      </c>
-      <c r="K100" s="3">
-        <v>3116751243</v>
-      </c>
-      <c r="L100" s="3">
-        <v>4530260427</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>294</v>
+        <v>4466039691</v>
+      </c>
+      <c r="P100" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.2">
@@ -3815,43 +3851,19 @@
         <v>112</v>
       </c>
       <c r="B101" s="11">
-        <v>1563383294</v>
+        <v>1626838871</v>
       </c>
       <c r="C101" s="3">
-        <v>4445938219</v>
+        <v>3941771000</v>
       </c>
       <c r="D101" s="3">
-        <v>4445942034</v>
+        <v>4353320440</v>
       </c>
       <c r="E101" s="3">
-        <v>4752034091</v>
-      </c>
-      <c r="F101" s="3">
-        <v>4158566592</v>
-      </c>
-      <c r="G101" s="3">
-        <v>4155960235</v>
-      </c>
-      <c r="H101" s="3">
-        <v>3795459019</v>
-      </c>
-      <c r="I101" s="3">
-        <v>3189692700</v>
-      </c>
-      <c r="J101" s="3">
-        <v>3192427748</v>
-      </c>
-      <c r="K101" s="3">
-        <v>2585328859</v>
-      </c>
-      <c r="L101" s="3">
-        <v>3116747411</v>
-      </c>
-      <c r="M101" s="3">
-        <v>4530263860</v>
-      </c>
-      <c r="P101" s="6" t="s">
-        <v>294</v>
+        <v>4466044425</v>
+      </c>
+      <c r="P101" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.2">
@@ -3859,34 +3871,28 @@
         <v>113</v>
       </c>
       <c r="B102" s="11">
-        <v>1625046334</v>
+        <v>1626838489</v>
       </c>
       <c r="C102" s="3">
-        <v>4445950675</v>
+        <v>4445937185</v>
       </c>
       <c r="D102" s="3">
-        <v>4445941119</v>
+        <v>4445941514</v>
       </c>
       <c r="E102" s="3">
-        <v>4155958279</v>
+        <v>3795459283</v>
       </c>
       <c r="F102" s="3">
-        <v>3941709950</v>
+        <v>4752031811</v>
       </c>
       <c r="G102" s="3">
-        <v>3795459634</v>
+        <v>4158567853</v>
       </c>
       <c r="H102" s="3">
-        <v>4752030098</v>
-      </c>
-      <c r="I102" s="3">
-        <v>4158566136</v>
-      </c>
-      <c r="J102" s="3">
-        <v>4466037745</v>
+        <v>4155958460</v>
       </c>
       <c r="P102" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.2">
@@ -3894,31 +3900,34 @@
         <v>114</v>
       </c>
       <c r="B103" s="11">
-        <v>1625046271</v>
+        <v>1626838716</v>
       </c>
       <c r="C103" s="3">
-        <v>4445958574</v>
+        <v>4445932146</v>
       </c>
       <c r="D103" s="3">
-        <v>4445942120</v>
+        <v>4445935099</v>
       </c>
       <c r="E103" s="3">
-        <v>4752032489</v>
+        <v>3795463857</v>
       </c>
       <c r="F103" s="3">
-        <v>4158565875</v>
+        <v>3941732373</v>
       </c>
       <c r="G103" s="3">
-        <v>4155957041</v>
+        <v>4752032943</v>
       </c>
       <c r="H103" s="3">
-        <v>3795462734</v>
+        <v>4158566388</v>
       </c>
       <c r="I103" s="3">
-        <v>4466038409</v>
+        <v>4155958134</v>
+      </c>
+      <c r="J103" s="3">
+        <v>4466038399</v>
       </c>
       <c r="P103" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.2">
@@ -3926,40 +3935,31 @@
         <v>115</v>
       </c>
       <c r="B104" s="11">
-        <v>1625046227</v>
+        <v>1626838872</v>
       </c>
       <c r="C104" s="3">
-        <v>4445932577</v>
+        <v>4445933330</v>
       </c>
       <c r="D104" s="3">
-        <v>4445943218</v>
+        <v>4445934571</v>
       </c>
       <c r="E104" s="3">
-        <v>3795461973</v>
+        <v>4752031660</v>
       </c>
       <c r="F104" s="3">
-        <v>3863596639</v>
+        <v>4158565874</v>
       </c>
       <c r="G104" s="3">
-        <v>3941704155</v>
+        <v>4155958635</v>
       </c>
       <c r="H104" s="3">
-        <v>4023852927</v>
+        <v>3795462745</v>
       </c>
       <c r="I104" s="3">
-        <v>4752031588</v>
-      </c>
-      <c r="J104" s="3">
-        <v>4158567200</v>
-      </c>
-      <c r="K104" s="3">
-        <v>4155960192</v>
-      </c>
-      <c r="L104" s="3">
-        <v>4466036877</v>
+        <v>4466035620</v>
       </c>
       <c r="P104" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.2">
@@ -3967,19 +3967,16 @@
         <v>116</v>
       </c>
       <c r="B105" s="11">
-        <v>1625046247</v>
+        <v>1626838767</v>
       </c>
       <c r="C105" s="3">
-        <v>3941704334</v>
+        <v>4353323144</v>
       </c>
       <c r="D105" s="3">
-        <v>4353363603</v>
-      </c>
-      <c r="E105" s="3">
-        <v>4466038208</v>
+        <v>4466037932</v>
       </c>
       <c r="P105" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.2">
@@ -3987,34 +3984,34 @@
         <v>117</v>
       </c>
       <c r="B106" s="11">
-        <v>1625046385</v>
+        <v>1626838847</v>
       </c>
       <c r="C106" s="3">
-        <v>4445936896</v>
+        <v>4445943187</v>
       </c>
       <c r="D106" s="3">
-        <v>4445946886</v>
+        <v>4445955638</v>
       </c>
       <c r="E106" s="3">
-        <v>3795460892</v>
+        <v>3941712763</v>
       </c>
       <c r="F106" s="3">
-        <v>4155957539</v>
+        <v>4752033686</v>
       </c>
       <c r="G106" s="3">
-        <v>3941704822</v>
+        <v>4158566982</v>
       </c>
       <c r="H106" s="3">
-        <v>4752029020</v>
+        <v>4155957621</v>
       </c>
       <c r="I106" s="3">
-        <v>4158565627</v>
+        <v>3795462705</v>
       </c>
       <c r="J106" s="3">
-        <v>4466035346</v>
+        <v>4466035884</v>
       </c>
       <c r="P106" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.2">
@@ -4022,31 +4019,19 @@
         <v>118</v>
       </c>
       <c r="B107" s="11">
-        <v>1625046276</v>
+        <v>1626838664</v>
       </c>
       <c r="C107" s="3">
-        <v>4445948495</v>
+        <v>3941722555</v>
       </c>
       <c r="D107" s="3">
-        <v>4445956474</v>
+        <v>4353313022</v>
       </c>
       <c r="E107" s="3">
-        <v>3795461021</v>
-      </c>
-      <c r="F107" s="3">
-        <v>4752030559</v>
-      </c>
-      <c r="G107" s="3">
-        <v>4158567951</v>
-      </c>
-      <c r="H107" s="3">
-        <v>4155958011</v>
-      </c>
-      <c r="I107" s="3">
-        <v>4466037689</v>
+        <v>4466037746</v>
       </c>
       <c r="P107" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.2">
@@ -4054,34 +4039,31 @@
         <v>119</v>
       </c>
       <c r="B108" s="11">
-        <v>1625046309</v>
+        <v>1626838959</v>
       </c>
       <c r="C108" s="3">
-        <v>4445953866</v>
+        <v>4445934096</v>
       </c>
       <c r="D108" s="3">
-        <v>4445944622</v>
+        <v>4445935044</v>
       </c>
       <c r="E108" s="3">
-        <v>3795461754</v>
+        <v>4155958097</v>
       </c>
       <c r="F108" s="3">
-        <v>4155959060</v>
+        <v>3795462221</v>
       </c>
       <c r="G108" s="3">
-        <v>3941714329</v>
+        <v>4752034118</v>
       </c>
       <c r="H108" s="3">
-        <v>4752027970</v>
+        <v>4158567084</v>
       </c>
       <c r="I108" s="3">
-        <v>4158567627</v>
-      </c>
-      <c r="J108" s="3">
-        <v>4466038522</v>
+        <v>4466035006</v>
       </c>
       <c r="P108" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.2">
@@ -4089,49 +4071,31 @@
         <v>120</v>
       </c>
       <c r="B109" s="11">
-        <v>1625431183</v>
+        <v>1626838955</v>
       </c>
       <c r="C109" s="3">
-        <v>4445939379</v>
+        <v>4445935899</v>
       </c>
       <c r="D109" s="3">
-        <v>4445944074</v>
+        <v>4445950677</v>
       </c>
       <c r="E109" s="3">
-        <v>3795460373</v>
+        <v>4155956830</v>
       </c>
       <c r="F109" s="3">
-        <v>4752029752</v>
+        <v>3795462053</v>
       </c>
       <c r="G109" s="3">
-        <v>4158565677</v>
+        <v>4752028370</v>
       </c>
       <c r="H109" s="3">
-        <v>4155959485</v>
+        <v>4158567246</v>
       </c>
       <c r="I109" s="3">
-        <v>4538028555</v>
-      </c>
-      <c r="J109" s="3">
-        <v>4661815305</v>
-      </c>
-      <c r="K109" s="3">
-        <v>4529511202</v>
-      </c>
-      <c r="L109" s="3">
-        <v>4600377356</v>
-      </c>
-      <c r="M109" s="3">
-        <v>4691614999</v>
-      </c>
-      <c r="N109" s="3">
-        <v>4413868976</v>
-      </c>
-      <c r="O109" s="3">
-        <v>4466043329</v>
+        <v>4466038937</v>
       </c>
       <c r="P109" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.2">
@@ -4139,16 +4103,31 @@
         <v>121</v>
       </c>
       <c r="B110" s="11">
-        <v>1625431121</v>
+        <v>1626838712</v>
       </c>
       <c r="C110" s="3">
-        <v>4752031641</v>
+        <v>4445942955</v>
       </c>
       <c r="D110" s="3">
-        <v>4466037450</v>
+        <v>4445958034</v>
+      </c>
+      <c r="E110" s="3">
+        <v>3795462827</v>
+      </c>
+      <c r="F110" s="3">
+        <v>4752030249</v>
+      </c>
+      <c r="G110" s="3">
+        <v>4158566647</v>
+      </c>
+      <c r="H110" s="3">
+        <v>4155956950</v>
+      </c>
+      <c r="I110" s="3">
+        <v>4466038455</v>
       </c>
       <c r="P110" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.2">
@@ -4156,34 +4135,40 @@
         <v>122</v>
       </c>
       <c r="B111" s="11">
-        <v>1625431048</v>
+        <v>1725971725</v>
       </c>
       <c r="C111" s="3">
-        <v>4445946589</v>
+        <v>4445940065</v>
       </c>
       <c r="D111" s="3">
-        <v>4445943627</v>
+        <v>4445936928</v>
       </c>
       <c r="E111" s="3">
-        <v>3795461182</v>
+        <v>4155957937</v>
       </c>
       <c r="F111" s="3">
-        <v>3941713769</v>
+        <v>3941705961</v>
       </c>
       <c r="G111" s="3">
-        <v>4752032880</v>
+        <v>4752032528</v>
       </c>
       <c r="H111" s="3">
-        <v>4158566145</v>
+        <v>4158566218</v>
       </c>
       <c r="I111" s="3">
-        <v>4155958972</v>
+        <v>3795456333</v>
       </c>
       <c r="J111" s="3">
-        <v>4466038473</v>
+        <v>3192429063</v>
+      </c>
+      <c r="K111" s="3">
+        <v>4530239729</v>
+      </c>
+      <c r="L111" s="3">
+        <v>4466037900</v>
       </c>
       <c r="P111" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.2">
@@ -4191,34 +4176,37 @@
         <v>123</v>
       </c>
       <c r="B112" s="11">
-        <v>1626838878</v>
+        <v>1738041026</v>
       </c>
       <c r="C112" s="3">
-        <v>4445947304</v>
+        <v>4445930804</v>
       </c>
       <c r="D112" s="3">
-        <v>4445950814</v>
+        <v>4445938488</v>
       </c>
       <c r="E112" s="3">
-        <v>4155958014</v>
+        <v>4752031128</v>
       </c>
       <c r="F112" s="3">
-        <v>3795464340</v>
+        <v>4158564689</v>
       </c>
       <c r="G112" s="3">
-        <v>4752030425</v>
+        <v>4155958123</v>
       </c>
       <c r="H112" s="3">
-        <v>4158568732</v>
+        <v>3795462804</v>
       </c>
       <c r="I112" s="3">
-        <v>4411164783</v>
+        <v>3189692797</v>
       </c>
       <c r="J112" s="3">
-        <v>4466039691</v>
+        <v>3192428192</v>
+      </c>
+      <c r="K112" s="3">
+        <v>4466038598</v>
       </c>
       <c r="P112" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.2">
@@ -4226,19 +4214,31 @@
         <v>124</v>
       </c>
       <c r="B113" s="11">
-        <v>1626838871</v>
+        <v>1738651525</v>
       </c>
       <c r="C113" s="3">
-        <v>3941771000</v>
+        <v>4445929126</v>
       </c>
       <c r="D113" s="3">
-        <v>4353320440</v>
+        <v>4445934796</v>
       </c>
       <c r="E113" s="3">
-        <v>4466044425</v>
+        <v>4752030632</v>
+      </c>
+      <c r="F113" s="3">
+        <v>4158559108</v>
+      </c>
+      <c r="G113" s="3">
+        <v>4155957296</v>
+      </c>
+      <c r="H113" s="3">
+        <v>3795460647</v>
+      </c>
+      <c r="I113" s="3">
+        <v>4466035504</v>
       </c>
       <c r="P113" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.2">
@@ -4246,28 +4246,37 @@
         <v>125</v>
       </c>
       <c r="B114" s="11">
-        <v>1626838489</v>
+        <v>1738652819</v>
       </c>
       <c r="C114" s="3">
-        <v>4445937185</v>
+        <v>4445936321</v>
       </c>
       <c r="D114" s="3">
-        <v>4445941514</v>
+        <v>4445932846</v>
       </c>
       <c r="E114" s="3">
-        <v>3795459283</v>
+        <v>4752033779</v>
       </c>
       <c r="F114" s="3">
-        <v>4752031811</v>
+        <v>4158566152</v>
       </c>
       <c r="G114" s="3">
-        <v>4158567853</v>
+        <v>4155958205</v>
       </c>
       <c r="H114" s="3">
-        <v>4155958460</v>
+        <v>3795464021</v>
+      </c>
+      <c r="I114" s="3">
+        <v>4515123549</v>
+      </c>
+      <c r="J114" s="3">
+        <v>4724083412</v>
+      </c>
+      <c r="K114" s="3">
+        <v>4466036190</v>
       </c>
       <c r="P114" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.2">
@@ -4275,34 +4284,40 @@
         <v>126</v>
       </c>
       <c r="B115" s="11">
-        <v>1626838716</v>
+        <v>1738652561</v>
       </c>
       <c r="C115" s="3">
-        <v>4445932146</v>
+        <v>4445960127</v>
       </c>
       <c r="D115" s="3">
-        <v>4445935099</v>
+        <v>4445949981</v>
       </c>
       <c r="E115" s="3">
-        <v>3795463857</v>
+        <v>3941772096</v>
       </c>
       <c r="F115" s="3">
-        <v>3941732373</v>
+        <v>4752032009</v>
       </c>
       <c r="G115" s="3">
-        <v>4752032943</v>
+        <v>4158565967</v>
       </c>
       <c r="H115" s="3">
-        <v>4158566388</v>
+        <v>4155960062</v>
       </c>
       <c r="I115" s="3">
-        <v>4155958134</v>
+        <v>3795460814</v>
       </c>
       <c r="J115" s="3">
-        <v>4466038399</v>
+        <v>3189693546</v>
+      </c>
+      <c r="K115" s="3">
+        <v>3192428372</v>
+      </c>
+      <c r="L115" s="3">
+        <v>4466035863</v>
       </c>
       <c r="P115" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.2">
@@ -4310,31 +4325,40 @@
         <v>127</v>
       </c>
       <c r="B116" s="11">
-        <v>1626838872</v>
+        <v>1738651871</v>
       </c>
       <c r="C116" s="3">
-        <v>4445933330</v>
+        <v>4445941388</v>
       </c>
       <c r="D116" s="3">
-        <v>4445934571</v>
+        <v>4445929150</v>
       </c>
       <c r="E116" s="3">
-        <v>4752031660</v>
+        <v>3795460731</v>
       </c>
       <c r="F116" s="3">
-        <v>4158565874</v>
+        <v>4155959773</v>
       </c>
       <c r="G116" s="3">
-        <v>4155958635</v>
+        <v>4752031752</v>
       </c>
       <c r="H116" s="3">
-        <v>3795462745</v>
+        <v>4158567672</v>
       </c>
       <c r="I116" s="3">
-        <v>4466035620</v>
+        <v>3189692444</v>
+      </c>
+      <c r="J116" s="3">
+        <v>3192428774</v>
+      </c>
+      <c r="K116" s="3">
+        <v>4530243679</v>
+      </c>
+      <c r="L116" s="3">
+        <v>4466036686</v>
       </c>
       <c r="P116" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.2">
@@ -4342,16 +4366,40 @@
         <v>128</v>
       </c>
       <c r="B117" s="11">
-        <v>1626838767</v>
+        <v>1738652486</v>
       </c>
       <c r="C117" s="3">
-        <v>4353323144</v>
+        <v>4445942012</v>
       </c>
       <c r="D117" s="3">
-        <v>4466037932</v>
+        <v>4445940063</v>
+      </c>
+      <c r="E117" s="3">
+        <v>3795460767</v>
+      </c>
+      <c r="F117" s="3">
+        <v>4752030861</v>
+      </c>
+      <c r="G117" s="3">
+        <v>4158565683</v>
+      </c>
+      <c r="H117" s="3">
+        <v>4155959291</v>
+      </c>
+      <c r="I117" s="3">
+        <v>3189693747</v>
+      </c>
+      <c r="J117" s="3">
+        <v>3192429002</v>
+      </c>
+      <c r="K117" s="3">
+        <v>4530234958</v>
+      </c>
+      <c r="L117" s="3">
+        <v>4466037441</v>
       </c>
       <c r="P117" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.2">
@@ -4359,34 +4407,40 @@
         <v>129</v>
       </c>
       <c r="B118" s="11">
-        <v>1626838847</v>
+        <v>1738652399</v>
       </c>
       <c r="C118" s="3">
-        <v>4445943187</v>
+        <v>4445930057</v>
       </c>
       <c r="D118" s="3">
-        <v>4445955638</v>
+        <v>4445932108</v>
       </c>
       <c r="E118" s="3">
-        <v>3941712763</v>
+        <v>3795461525</v>
       </c>
       <c r="F118" s="3">
-        <v>4752033686</v>
+        <v>3941698250</v>
       </c>
       <c r="G118" s="3">
-        <v>4158566982</v>
+        <v>4752035948</v>
       </c>
       <c r="H118" s="3">
-        <v>4155957621</v>
+        <v>4155959053</v>
       </c>
       <c r="I118" s="3">
-        <v>3795462705</v>
+        <v>4158565737</v>
       </c>
       <c r="J118" s="3">
-        <v>4466035884</v>
+        <v>3189694531</v>
+      </c>
+      <c r="K118" s="3">
+        <v>3192428834</v>
+      </c>
+      <c r="L118" s="3">
+        <v>4466038631</v>
       </c>
       <c r="P118" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.2">
@@ -4394,19 +4448,13 @@
         <v>130</v>
       </c>
       <c r="B119" s="11">
-        <v>1626838664</v>
-      </c>
-      <c r="C119" s="3">
-        <v>3941722555</v>
-      </c>
-      <c r="D119" s="3">
-        <v>4353313022</v>
-      </c>
-      <c r="E119" s="3">
-        <v>4466037746</v>
+        <v>2449977972</v>
+      </c>
+      <c r="C119" s="5">
+        <v>3795497894</v>
       </c>
       <c r="P119" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.2">
@@ -4414,31 +4462,16 @@
         <v>131</v>
       </c>
       <c r="B120" s="11">
-        <v>1626838959</v>
+        <v>2449976830</v>
       </c>
       <c r="C120" s="3">
-        <v>4445934096</v>
+        <v>3795498228</v>
       </c>
       <c r="D120" s="3">
-        <v>4445935044</v>
-      </c>
-      <c r="E120" s="3">
-        <v>4155958097</v>
-      </c>
-      <c r="F120" s="3">
-        <v>3795462221</v>
-      </c>
-      <c r="G120" s="3">
-        <v>4752034118</v>
-      </c>
-      <c r="H120" s="3">
-        <v>4158567084</v>
-      </c>
-      <c r="I120" s="3">
-        <v>4466035006</v>
+        <v>4411172564</v>
       </c>
       <c r="P120" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.2">
@@ -4446,31 +4479,10 @@
         <v>132</v>
       </c>
       <c r="B121" s="11">
-        <v>1626838955</v>
-      </c>
-      <c r="C121" s="3">
-        <v>4445935899</v>
-      </c>
-      <c r="D121" s="3">
-        <v>4445950677</v>
-      </c>
-      <c r="E121" s="3">
-        <v>4155956830</v>
-      </c>
-      <c r="F121" s="3">
-        <v>3795462053</v>
-      </c>
-      <c r="G121" s="3">
-        <v>4752028370</v>
-      </c>
-      <c r="H121" s="3">
-        <v>4158567246</v>
-      </c>
-      <c r="I121" s="3">
-        <v>4466038937</v>
+        <v>2449978285</v>
       </c>
       <c r="P121" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.2">
@@ -4478,31 +4490,25 @@
         <v>133</v>
       </c>
       <c r="B122" s="11">
-        <v>1626838712</v>
+        <v>2449978096</v>
       </c>
       <c r="C122" s="3">
-        <v>4445942955</v>
+        <v>4027388111</v>
       </c>
       <c r="D122" s="3">
-        <v>4445958034</v>
+        <v>4027405448</v>
       </c>
       <c r="E122" s="3">
-        <v>3795462827</v>
+        <v>3795494657</v>
       </c>
       <c r="F122" s="3">
-        <v>4752030249</v>
+        <v>4411169009</v>
       </c>
       <c r="G122" s="3">
-        <v>4158566647</v>
-      </c>
-      <c r="H122" s="3">
-        <v>4155956950</v>
-      </c>
-      <c r="I122" s="3">
-        <v>4466038455</v>
+        <v>4411169009</v>
       </c>
       <c r="P122" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.2">
@@ -4510,40 +4516,13 @@
         <v>134</v>
       </c>
       <c r="B123" s="11">
-        <v>1725971725</v>
+        <v>2449977830</v>
       </c>
       <c r="C123" s="3">
-        <v>4445940065</v>
-      </c>
-      <c r="D123" s="3">
-        <v>4445936928</v>
-      </c>
-      <c r="E123" s="3">
-        <v>4155957937</v>
-      </c>
-      <c r="F123" s="3">
-        <v>3941705961</v>
-      </c>
-      <c r="G123" s="3">
-        <v>4752032528</v>
-      </c>
-      <c r="H123" s="3">
-        <v>4158566218</v>
-      </c>
-      <c r="I123" s="3">
-        <v>3795456333</v>
-      </c>
-      <c r="J123" s="3">
-        <v>3192429063</v>
-      </c>
-      <c r="K123" s="3">
-        <v>4530239729</v>
-      </c>
-      <c r="L123" s="3">
-        <v>4466037900</v>
+        <v>3795498107</v>
       </c>
       <c r="P123" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.2">
@@ -4551,37 +4530,13 @@
         <v>135</v>
       </c>
       <c r="B124" s="11">
-        <v>1738041026</v>
-      </c>
-      <c r="C124" s="3">
-        <v>4445930804</v>
-      </c>
-      <c r="D124" s="3">
-        <v>4445938488</v>
-      </c>
-      <c r="E124" s="3">
-        <v>4752031128</v>
-      </c>
-      <c r="F124" s="3">
-        <v>4158564689</v>
-      </c>
-      <c r="G124" s="3">
-        <v>4155958123</v>
-      </c>
-      <c r="H124" s="3">
-        <v>3795462804</v>
-      </c>
-      <c r="I124" s="3">
-        <v>3189692797</v>
-      </c>
-      <c r="J124" s="3">
-        <v>3192428192</v>
-      </c>
-      <c r="K124" s="3">
-        <v>4466038598</v>
+        <v>2449979383</v>
+      </c>
+      <c r="C124" s="5">
+        <v>4411169482</v>
       </c>
       <c r="P124" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.2">
@@ -4589,31 +4544,16 @@
         <v>136</v>
       </c>
       <c r="B125" s="11">
-        <v>1738651525</v>
+        <v>2449977151</v>
       </c>
       <c r="C125" s="3">
-        <v>4445929126</v>
+        <v>3795497444</v>
       </c>
       <c r="D125" s="3">
-        <v>4445934796</v>
-      </c>
-      <c r="E125" s="3">
-        <v>4752030632</v>
-      </c>
-      <c r="F125" s="3">
-        <v>4158559108</v>
-      </c>
-      <c r="G125" s="3">
-        <v>4155957296</v>
-      </c>
-      <c r="H125" s="3">
-        <v>3795460647</v>
-      </c>
-      <c r="I125" s="3">
-        <v>4466035504</v>
+        <v>4411163271</v>
       </c>
       <c r="P125" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.2">
@@ -4621,37 +4561,16 @@
         <v>137</v>
       </c>
       <c r="B126" s="11">
-        <v>1738652819</v>
-      </c>
-      <c r="C126" s="3">
-        <v>4445936321</v>
+        <v>2449977812</v>
+      </c>
+      <c r="C126" s="5">
+        <v>3795496728</v>
       </c>
       <c r="D126" s="3">
-        <v>4445932846</v>
-      </c>
-      <c r="E126" s="3">
-        <v>4752033779</v>
-      </c>
-      <c r="F126" s="3">
-        <v>4158566152</v>
-      </c>
-      <c r="G126" s="3">
-        <v>4155958205</v>
-      </c>
-      <c r="H126" s="3">
-        <v>3795464021</v>
-      </c>
-      <c r="I126" s="3">
-        <v>4515123549</v>
-      </c>
-      <c r="J126" s="3">
-        <v>4724083412</v>
-      </c>
-      <c r="K126" s="3">
-        <v>4466036190</v>
+        <v>4411169394</v>
       </c>
       <c r="P126" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.2">
@@ -4659,40 +4578,13 @@
         <v>138</v>
       </c>
       <c r="B127" s="11">
-        <v>1738652561</v>
+        <v>2449977848</v>
       </c>
       <c r="C127" s="3">
-        <v>4445960127</v>
-      </c>
-      <c r="D127" s="3">
-        <v>4445949981</v>
-      </c>
-      <c r="E127" s="3">
-        <v>3941772096</v>
-      </c>
-      <c r="F127" s="3">
-        <v>4752032009</v>
-      </c>
-      <c r="G127" s="3">
-        <v>4158565967</v>
-      </c>
-      <c r="H127" s="3">
-        <v>4155960062</v>
-      </c>
-      <c r="I127" s="3">
-        <v>3795460814</v>
-      </c>
-      <c r="J127" s="3">
-        <v>3189693546</v>
-      </c>
-      <c r="K127" s="3">
-        <v>3192428372</v>
-      </c>
-      <c r="L127" s="3">
-        <v>4466035863</v>
+        <v>4411164044</v>
       </c>
       <c r="P127" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.2">
@@ -4700,40 +4592,13 @@
         <v>139</v>
       </c>
       <c r="B128" s="11">
-        <v>1738651871</v>
+        <v>2449977623</v>
       </c>
       <c r="C128" s="3">
-        <v>4445941388</v>
-      </c>
-      <c r="D128" s="3">
-        <v>4445929150</v>
-      </c>
-      <c r="E128" s="3">
-        <v>3795460731</v>
-      </c>
-      <c r="F128" s="3">
-        <v>4155959773</v>
-      </c>
-      <c r="G128" s="3">
-        <v>4752031752</v>
-      </c>
-      <c r="H128" s="3">
-        <v>4158567672</v>
-      </c>
-      <c r="I128" s="3">
-        <v>3189692444</v>
-      </c>
-      <c r="J128" s="3">
-        <v>3192428774</v>
-      </c>
-      <c r="K128" s="3">
-        <v>4530243679</v>
-      </c>
-      <c r="L128" s="3">
-        <v>4466036686</v>
+        <v>3795498609</v>
       </c>
       <c r="P128" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.2">
@@ -4741,40 +4606,13 @@
         <v>140</v>
       </c>
       <c r="B129" s="11">
-        <v>1738652486</v>
+        <v>2449976760</v>
       </c>
       <c r="C129" s="3">
-        <v>4445942012</v>
-      </c>
-      <c r="D129" s="3">
-        <v>4445940063</v>
-      </c>
-      <c r="E129" s="3">
-        <v>3795460767</v>
-      </c>
-      <c r="F129" s="3">
-        <v>4752030861</v>
-      </c>
-      <c r="G129" s="3">
-        <v>4158565683</v>
-      </c>
-      <c r="H129" s="3">
-        <v>4155959291</v>
-      </c>
-      <c r="I129" s="3">
-        <v>3189693747</v>
-      </c>
-      <c r="J129" s="3">
-        <v>3192429002</v>
-      </c>
-      <c r="K129" s="3">
-        <v>4530234958</v>
-      </c>
-      <c r="L129" s="3">
-        <v>4466037441</v>
+        <v>4411169474</v>
       </c>
       <c r="P129" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.2">
@@ -4782,40 +4620,16 @@
         <v>141</v>
       </c>
       <c r="B130" s="11">
-        <v>1738652399</v>
+        <v>2449978556</v>
       </c>
       <c r="C130" s="3">
-        <v>4445930057</v>
+        <v>3795497196</v>
       </c>
       <c r="D130" s="3">
-        <v>4445932108</v>
-      </c>
-      <c r="E130" s="3">
-        <v>3795461525</v>
-      </c>
-      <c r="F130" s="3">
-        <v>3941698250</v>
-      </c>
-      <c r="G130" s="3">
-        <v>4752035948</v>
-      </c>
-      <c r="H130" s="3">
-        <v>4155959053</v>
-      </c>
-      <c r="I130" s="3">
-        <v>4158565737</v>
-      </c>
-      <c r="J130" s="3">
-        <v>3189694531</v>
-      </c>
-      <c r="K130" s="3">
-        <v>3192428834</v>
-      </c>
-      <c r="L130" s="3">
-        <v>4466038631</v>
+        <v>4411162694</v>
       </c>
       <c r="P130" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.2">
@@ -4823,13 +4637,19 @@
         <v>142</v>
       </c>
       <c r="B131" s="11">
-        <v>2449977972</v>
-      </c>
-      <c r="C131" s="5">
-        <v>3795497894</v>
+        <v>2449976743</v>
+      </c>
+      <c r="C131" s="3">
+        <v>3795496684</v>
+      </c>
+      <c r="D131" s="3">
+        <v>4411169486</v>
+      </c>
+      <c r="E131" s="3">
+        <v>4724087547</v>
       </c>
       <c r="P131" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.2">
@@ -4837,16 +4657,16 @@
         <v>143</v>
       </c>
       <c r="B132" s="11">
-        <v>2449976830</v>
+        <v>2449977121</v>
       </c>
       <c r="C132" s="3">
-        <v>3795498228</v>
+        <v>3795495353</v>
       </c>
       <c r="D132" s="3">
-        <v>4411172564</v>
+        <v>4411169297</v>
       </c>
       <c r="P132" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.2">
@@ -4854,10 +4674,16 @@
         <v>144</v>
       </c>
       <c r="B133" s="11">
-        <v>2449978285</v>
+        <v>2449976996</v>
+      </c>
+      <c r="C133" s="3">
+        <v>3795495820</v>
+      </c>
+      <c r="D133" s="3">
+        <v>4724083911</v>
       </c>
       <c r="P133" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.2">
@@ -4865,25 +4691,13 @@
         <v>145</v>
       </c>
       <c r="B134" s="11">
-        <v>2449978096</v>
+        <v>2449976986</v>
       </c>
       <c r="C134" s="3">
-        <v>4027388111</v>
-      </c>
-      <c r="D134" s="3">
-        <v>4027405448</v>
-      </c>
-      <c r="E134" s="3">
-        <v>3795494657</v>
-      </c>
-      <c r="F134" s="3">
-        <v>4411169009</v>
-      </c>
-      <c r="G134" s="3">
-        <v>4411169009</v>
+        <v>3795497092</v>
       </c>
       <c r="P134" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.2">
@@ -4891,13 +4705,13 @@
         <v>146</v>
       </c>
       <c r="B135" s="11">
-        <v>2449977830</v>
+        <v>2449979595</v>
       </c>
       <c r="C135" s="3">
-        <v>3795498107</v>
+        <v>3795498347</v>
       </c>
       <c r="P135" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.2">
@@ -4905,13 +4719,13 @@
         <v>147</v>
       </c>
       <c r="B136" s="11">
-        <v>2449979383</v>
-      </c>
-      <c r="C136" s="5">
-        <v>4411169482</v>
+        <v>2449977394</v>
+      </c>
+      <c r="C136" s="3">
+        <v>3795497485</v>
       </c>
       <c r="P136" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.2">
@@ -4919,16 +4733,19 @@
         <v>148</v>
       </c>
       <c r="B137" s="11">
-        <v>2449977151</v>
+        <v>2449978533</v>
       </c>
       <c r="C137" s="3">
-        <v>3795497444</v>
+        <v>3795494919</v>
       </c>
       <c r="D137" s="3">
-        <v>4411163271</v>
+        <v>3351397301</v>
+      </c>
+      <c r="E137" s="3">
+        <v>4411171336</v>
       </c>
       <c r="P137" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.2">
@@ -4936,16 +4753,19 @@
         <v>149</v>
       </c>
       <c r="B138" s="11">
-        <v>2449977812</v>
-      </c>
-      <c r="C138" s="5">
-        <v>3795496728</v>
+        <v>2449977131</v>
+      </c>
+      <c r="C138" s="3">
+        <v>3795497460</v>
       </c>
       <c r="D138" s="3">
-        <v>4411169394</v>
+        <v>4724099263</v>
+      </c>
+      <c r="E138" s="3">
+        <v>4724101883</v>
       </c>
       <c r="P138" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.2">
@@ -4953,13 +4773,13 @@
         <v>150</v>
       </c>
       <c r="B139" s="11">
-        <v>2449977848</v>
+        <v>2449977197</v>
       </c>
       <c r="C139" s="3">
-        <v>4411164044</v>
+        <v>3795496938</v>
       </c>
       <c r="P139" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.2">
@@ -4967,13 +4787,16 @@
         <v>151</v>
       </c>
       <c r="B140" s="11">
-        <v>2449977623</v>
+        <v>2449977033</v>
       </c>
       <c r="C140" s="3">
-        <v>3795498609</v>
+        <v>4070277699</v>
+      </c>
+      <c r="D140" s="3">
+        <v>4411168663</v>
       </c>
       <c r="P140" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.2">
@@ -4981,13 +4804,13 @@
         <v>152</v>
       </c>
       <c r="B141" s="11">
-        <v>2449976760</v>
+        <v>2449977090</v>
       </c>
       <c r="C141" s="3">
-        <v>4411169474</v>
+        <v>3795498152</v>
       </c>
       <c r="P141" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.2">
@@ -4995,16 +4818,13 @@
         <v>153</v>
       </c>
       <c r="B142" s="11">
-        <v>2449978556</v>
+        <v>2449977863</v>
       </c>
       <c r="C142" s="3">
-        <v>3795497196</v>
-      </c>
-      <c r="D142" s="3">
-        <v>4411162694</v>
+        <v>3795498549</v>
       </c>
       <c r="P142" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.2">
@@ -5012,19 +4832,16 @@
         <v>154</v>
       </c>
       <c r="B143" s="11">
-        <v>2449976743</v>
+        <v>2449977838</v>
       </c>
       <c r="C143" s="3">
-        <v>3795496684</v>
+        <v>3795496898</v>
       </c>
       <c r="D143" s="3">
-        <v>4411169486</v>
-      </c>
-      <c r="E143" s="3">
-        <v>4724087547</v>
+        <v>4411169151</v>
       </c>
       <c r="P143" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.2">
@@ -5032,16 +4849,16 @@
         <v>155</v>
       </c>
       <c r="B144" s="11">
-        <v>2449977121</v>
+        <v>2449977504</v>
       </c>
       <c r="C144" s="3">
-        <v>3795495353</v>
+        <v>3795496191</v>
       </c>
       <c r="D144" s="3">
-        <v>4411169297</v>
+        <v>4411168817</v>
       </c>
       <c r="P144" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.2">
@@ -5049,16 +4866,16 @@
         <v>156</v>
       </c>
       <c r="B145" s="11">
-        <v>2449976996</v>
-      </c>
-      <c r="C145" s="3">
-        <v>3795495820</v>
+        <v>2449978674</v>
+      </c>
+      <c r="C145" s="5">
+        <v>3795500844</v>
       </c>
       <c r="D145" s="3">
-        <v>4724083911</v>
+        <v>4411163071</v>
       </c>
       <c r="P145" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.2">
@@ -5066,13 +4883,16 @@
         <v>157</v>
       </c>
       <c r="B146" s="11">
-        <v>2449976986</v>
+        <v>2449978115</v>
       </c>
       <c r="C146" s="3">
-        <v>3795497092</v>
+        <v>3795498528</v>
+      </c>
+      <c r="D146" s="3">
+        <v>4411169425</v>
       </c>
       <c r="P146" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.2">
@@ -5080,13 +4900,16 @@
         <v>158</v>
       </c>
       <c r="B147" s="11">
-        <v>2449979595</v>
+        <v>2449978809</v>
       </c>
       <c r="C147" s="3">
-        <v>3795498347</v>
+        <v>3795497296</v>
+      </c>
+      <c r="D147" s="3">
+        <v>4411169080</v>
       </c>
       <c r="P147" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.2">
@@ -5094,13 +4917,16 @@
         <v>159</v>
       </c>
       <c r="B148" s="11">
-        <v>2449977394</v>
+        <v>2449978546</v>
       </c>
       <c r="C148" s="3">
-        <v>3795497485</v>
+        <v>4691410471</v>
+      </c>
+      <c r="D148" s="3">
+        <v>4411167390</v>
       </c>
       <c r="P148" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.2">
@@ -5108,19 +4934,16 @@
         <v>160</v>
       </c>
       <c r="B149" s="11">
-        <v>2449978533</v>
+        <v>2449981733</v>
       </c>
       <c r="C149" s="3">
-        <v>3795494919</v>
+        <v>3795498358</v>
       </c>
       <c r="D149" s="3">
-        <v>3351397301</v>
-      </c>
-      <c r="E149" s="3">
-        <v>4411171336</v>
+        <v>4411163514</v>
       </c>
       <c r="P149" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.2">
@@ -5128,19 +4951,22 @@
         <v>161</v>
       </c>
       <c r="B150" s="11">
-        <v>2449977131</v>
+        <v>2449977019</v>
       </c>
       <c r="C150" s="3">
-        <v>3795497460</v>
+        <v>3795498360</v>
       </c>
       <c r="D150" s="3">
-        <v>4724099263</v>
+        <v>4411169568</v>
       </c>
       <c r="E150" s="3">
-        <v>4724101883</v>
+        <v>4471245118</v>
+      </c>
+      <c r="F150" s="3">
+        <v>4443059125</v>
       </c>
       <c r="P150" s="7" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.2">
@@ -5148,13 +4974,13 @@
         <v>162</v>
       </c>
       <c r="B151" s="11">
-        <v>2449977197</v>
+        <v>2474254088</v>
       </c>
       <c r="C151" s="3">
-        <v>3795496938</v>
-      </c>
-      <c r="P151" s="7" t="s">
-        <v>296</v>
+        <v>4410795843</v>
+      </c>
+      <c r="P151" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.2">
@@ -5162,16 +4988,13 @@
         <v>163</v>
       </c>
       <c r="B152" s="11">
-        <v>2449977033</v>
+        <v>2474251681</v>
       </c>
       <c r="C152" s="3">
-        <v>4070277699</v>
-      </c>
-      <c r="D152" s="3">
-        <v>4411168663</v>
-      </c>
-      <c r="P152" s="7" t="s">
-        <v>296</v>
+        <v>4410792899</v>
+      </c>
+      <c r="P152" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -5179,13 +5002,13 @@
         <v>164</v>
       </c>
       <c r="B153" s="11">
-        <v>2449977090</v>
+        <v>2474254458</v>
       </c>
       <c r="C153" s="3">
-        <v>3795498152</v>
-      </c>
-      <c r="P153" s="7" t="s">
-        <v>296</v>
+        <v>4410794178</v>
+      </c>
+      <c r="P153" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.2">
@@ -5193,13 +5016,13 @@
         <v>165</v>
       </c>
       <c r="B154" s="11">
-        <v>2449977863</v>
+        <v>2474254911</v>
       </c>
       <c r="C154" s="3">
-        <v>3795498549</v>
-      </c>
-      <c r="P154" s="7" t="s">
-        <v>296</v>
+        <v>4410794548</v>
+      </c>
+      <c r="P154" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.2">
@@ -5207,16 +5030,10 @@
         <v>166</v>
       </c>
       <c r="B155" s="11">
-        <v>2449977838</v>
-      </c>
-      <c r="C155" s="3">
-        <v>3795496898</v>
-      </c>
-      <c r="D155" s="3">
-        <v>4411169151</v>
-      </c>
-      <c r="P155" s="7" t="s">
-        <v>296</v>
+        <v>2474252885</v>
+      </c>
+      <c r="P155" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.2">
@@ -5224,16 +5041,13 @@
         <v>167</v>
       </c>
       <c r="B156" s="11">
-        <v>2449977504</v>
+        <v>2474252719</v>
       </c>
       <c r="C156" s="3">
-        <v>3795496191</v>
-      </c>
-      <c r="D156" s="3">
-        <v>4411168817</v>
-      </c>
-      <c r="P156" s="7" t="s">
-        <v>296</v>
+        <v>4410795061</v>
+      </c>
+      <c r="P156" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -5241,16 +5055,13 @@
         <v>168</v>
       </c>
       <c r="B157" s="11">
-        <v>2449978674</v>
+        <v>2474252861</v>
       </c>
       <c r="C157" s="5">
-        <v>3795500844</v>
-      </c>
-      <c r="D157" s="3">
-        <v>4411163071</v>
-      </c>
-      <c r="P157" s="7" t="s">
-        <v>296</v>
+        <v>4410794283</v>
+      </c>
+      <c r="P157" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.2">
@@ -5258,16 +5069,13 @@
         <v>169</v>
       </c>
       <c r="B158" s="11">
-        <v>2449978115</v>
+        <v>2474254639</v>
       </c>
       <c r="C158" s="3">
-        <v>3795498528</v>
-      </c>
-      <c r="D158" s="3">
-        <v>4411169425</v>
-      </c>
-      <c r="P158" s="7" t="s">
-        <v>296</v>
+        <v>4410793109</v>
+      </c>
+      <c r="P158" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.2">
@@ -5275,16 +5083,13 @@
         <v>170</v>
       </c>
       <c r="B159" s="11">
-        <v>2449978809</v>
+        <v>2474256003</v>
       </c>
       <c r="C159" s="3">
-        <v>3795497296</v>
-      </c>
-      <c r="D159" s="3">
-        <v>4411169080</v>
-      </c>
-      <c r="P159" s="7" t="s">
-        <v>296</v>
+        <v>4410794696</v>
+      </c>
+      <c r="P159" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.2">
@@ -5292,16 +5097,10 @@
         <v>171</v>
       </c>
       <c r="B160" s="11">
-        <v>2449978546</v>
-      </c>
-      <c r="C160" s="3">
-        <v>4691410471</v>
-      </c>
-      <c r="D160" s="3">
-        <v>4411167390</v>
-      </c>
-      <c r="P160" s="7" t="s">
-        <v>296</v>
+        <v>2474254390</v>
+      </c>
+      <c r="P160" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.2">
@@ -5309,16 +5108,10 @@
         <v>172</v>
       </c>
       <c r="B161" s="11">
-        <v>2449981733</v>
-      </c>
-      <c r="C161" s="3">
-        <v>3795498358</v>
-      </c>
-      <c r="D161" s="3">
-        <v>4411163514</v>
-      </c>
-      <c r="P161" s="7" t="s">
-        <v>296</v>
+        <v>2474254998</v>
+      </c>
+      <c r="P161" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.2">
@@ -5326,22 +5119,13 @@
         <v>173</v>
       </c>
       <c r="B162" s="11">
-        <v>2449977019</v>
+        <v>2474254021</v>
       </c>
       <c r="C162" s="3">
-        <v>3795498360</v>
-      </c>
-      <c r="D162" s="3">
-        <v>4411169568</v>
-      </c>
-      <c r="E162" s="3">
-        <v>4471245118</v>
-      </c>
-      <c r="F162" s="3">
-        <v>4443059125</v>
-      </c>
-      <c r="P162" s="7" t="s">
-        <v>296</v>
+        <v>4410796092</v>
+      </c>
+      <c r="P162" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="163" spans="1:16" x14ac:dyDescent="0.2">
@@ -5349,13 +5133,10 @@
         <v>174</v>
       </c>
       <c r="B163" s="11">
-        <v>2474254088</v>
-      </c>
-      <c r="C163" s="3">
-        <v>4410795843</v>
+        <v>2474251925</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.2">
@@ -5363,13 +5144,10 @@
         <v>175</v>
       </c>
       <c r="B164" s="11">
-        <v>2474251681</v>
-      </c>
-      <c r="C164" s="3">
-        <v>4410792899</v>
+        <v>2474254255</v>
       </c>
       <c r="P164" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.2">
@@ -5377,13 +5155,10 @@
         <v>176</v>
       </c>
       <c r="B165" s="11">
-        <v>2474254458</v>
-      </c>
-      <c r="C165" s="3">
-        <v>4410794178</v>
+        <v>2474254585</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.2">
@@ -5391,13 +5166,10 @@
         <v>177</v>
       </c>
       <c r="B166" s="11">
-        <v>2474254911</v>
-      </c>
-      <c r="C166" s="3">
-        <v>4410794548</v>
+        <v>2474252626</v>
       </c>
       <c r="P166" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.2">
@@ -5405,10 +5177,10 @@
         <v>178</v>
       </c>
       <c r="B167" s="11">
-        <v>2474252885</v>
+        <v>2474251481</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="168" spans="1:16" x14ac:dyDescent="0.2">
@@ -5416,13 +5188,13 @@
         <v>179</v>
       </c>
       <c r="B168" s="11">
-        <v>2474252719</v>
-      </c>
-      <c r="C168" s="3">
-        <v>4410795061</v>
+        <v>2474254579</v>
+      </c>
+      <c r="C168" s="5">
+        <v>4410793689</v>
       </c>
       <c r="P168" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.2">
@@ -5430,13 +5202,13 @@
         <v>180</v>
       </c>
       <c r="B169" s="11">
-        <v>2474252861</v>
-      </c>
-      <c r="C169" s="5">
-        <v>4410794283</v>
+        <v>2474255592</v>
+      </c>
+      <c r="C169" s="3">
+        <v>4410793826</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.2">
@@ -5444,13 +5216,13 @@
         <v>181</v>
       </c>
       <c r="B170" s="11">
-        <v>2474254639</v>
+        <v>2474254273</v>
       </c>
       <c r="C170" s="3">
-        <v>4410793109</v>
+        <v>4410794361</v>
       </c>
       <c r="P170" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="171" spans="1:16" x14ac:dyDescent="0.2">
@@ -5458,13 +5230,13 @@
         <v>182</v>
       </c>
       <c r="B171" s="11">
-        <v>2474256003</v>
+        <v>2474251571</v>
       </c>
       <c r="C171" s="3">
-        <v>4410794696</v>
+        <v>4410793497</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.2">
@@ -5472,10 +5244,13 @@
         <v>183</v>
       </c>
       <c r="B172" s="11">
-        <v>2474254390</v>
+        <v>2474253289</v>
+      </c>
+      <c r="C172" s="3">
+        <v>4410794492</v>
       </c>
       <c r="P172" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.2">
@@ -5483,10 +5258,13 @@
         <v>184</v>
       </c>
       <c r="B173" s="11">
-        <v>2474254998</v>
+        <v>2474252601</v>
+      </c>
+      <c r="C173" s="3">
+        <v>4410794643</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.2">
@@ -5494,13 +5272,10 @@
         <v>185</v>
       </c>
       <c r="B174" s="11">
-        <v>2474254021</v>
-      </c>
-      <c r="C174" s="3">
-        <v>4410796092</v>
+        <v>2474253325</v>
       </c>
       <c r="P174" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.2">
@@ -5508,10 +5283,10 @@
         <v>186</v>
       </c>
       <c r="B175" s="11">
-        <v>2474251925</v>
+        <v>2474253882</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.2">
@@ -5519,10 +5294,13 @@
         <v>187</v>
       </c>
       <c r="B176" s="11">
-        <v>2474254255</v>
+        <v>2474253913</v>
+      </c>
+      <c r="C176" s="3">
+        <v>4410793924</v>
       </c>
       <c r="P176" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.2">
@@ -5530,10 +5308,13 @@
         <v>188</v>
       </c>
       <c r="B177" s="11">
-        <v>2474254585</v>
+        <v>2474255236</v>
+      </c>
+      <c r="C177" s="3">
+        <v>4352308658</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.2">
@@ -5541,10 +5322,13 @@
         <v>189</v>
       </c>
       <c r="B178" s="11">
-        <v>2474252626</v>
+        <v>2474252891</v>
+      </c>
+      <c r="C178" s="3">
+        <v>4410793050</v>
       </c>
       <c r="P178" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.2">
@@ -5552,10 +5336,10 @@
         <v>190</v>
       </c>
       <c r="B179" s="11">
-        <v>2474251481</v>
+        <v>2474431127</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.2">
@@ -5563,13 +5347,16 @@
         <v>191</v>
       </c>
       <c r="B180" s="11">
-        <v>2474254579</v>
-      </c>
-      <c r="C180" s="5">
-        <v>4410793689</v>
+        <v>3691738336</v>
+      </c>
+      <c r="C180" s="3">
+        <v>4544763211</v>
+      </c>
+      <c r="D180" s="3">
+        <v>4086257096</v>
       </c>
       <c r="P180" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.2">
@@ -5577,13 +5364,13 @@
         <v>192</v>
       </c>
       <c r="B181" s="11">
-        <v>2474255592</v>
+        <v>3691841964</v>
       </c>
       <c r="C181" s="3">
-        <v>4410793826</v>
+        <v>4544759914</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.2">
@@ -5591,13 +5378,13 @@
         <v>193</v>
       </c>
       <c r="B182" s="11">
-        <v>2474254273</v>
+        <v>3691844921</v>
       </c>
       <c r="C182" s="3">
-        <v>4410794361</v>
+        <v>4544759944</v>
       </c>
       <c r="P182" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.2">
@@ -5605,13 +5392,16 @@
         <v>194</v>
       </c>
       <c r="B183" s="11">
-        <v>2474251571</v>
+        <v>3691842819</v>
       </c>
       <c r="C183" s="3">
-        <v>4410793497</v>
+        <v>4544752572</v>
+      </c>
+      <c r="D183" s="3">
+        <v>4086258895</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.2">
@@ -5619,13 +5409,16 @@
         <v>195</v>
       </c>
       <c r="B184" s="11">
-        <v>2474253289</v>
+        <v>3691843282</v>
       </c>
       <c r="C184" s="3">
-        <v>4410794492</v>
+        <v>4544775205</v>
+      </c>
+      <c r="D184" s="3">
+        <v>4086257286</v>
       </c>
       <c r="P184" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.2">
@@ -5633,13 +5426,16 @@
         <v>196</v>
       </c>
       <c r="B185" s="11">
-        <v>2474252601</v>
+        <v>3691843233</v>
       </c>
       <c r="C185" s="3">
-        <v>4410794643</v>
+        <v>4544751852</v>
+      </c>
+      <c r="D185" s="3">
+        <v>4086260262</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.2">
@@ -5647,10 +5443,16 @@
         <v>197</v>
       </c>
       <c r="B186" s="11">
-        <v>2474253325</v>
+        <v>3691843824</v>
+      </c>
+      <c r="C186" s="3">
+        <v>4544768940</v>
+      </c>
+      <c r="D186" s="3">
+        <v>4086264776</v>
       </c>
       <c r="P186" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.2">
@@ -5658,10 +5460,10 @@
         <v>198</v>
       </c>
       <c r="B187" s="11">
-        <v>2474253882</v>
+        <v>3691843469</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.2">
@@ -5669,13 +5471,16 @@
         <v>199</v>
       </c>
       <c r="B188" s="11">
-        <v>2474253913</v>
+        <v>3691843333</v>
       </c>
       <c r="C188" s="3">
-        <v>4410793924</v>
+        <v>4544769486</v>
+      </c>
+      <c r="D188" s="3">
+        <v>4086265043</v>
       </c>
       <c r="P188" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.2">
@@ -5683,13 +5488,10 @@
         <v>200</v>
       </c>
       <c r="B189" s="11">
-        <v>2474255236</v>
-      </c>
-      <c r="C189" s="3">
-        <v>4352308658</v>
+        <v>3691843790</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.2">
@@ -5697,13 +5499,16 @@
         <v>201</v>
       </c>
       <c r="B190" s="11">
-        <v>2474252891</v>
+        <v>3691842613</v>
       </c>
       <c r="C190" s="3">
-        <v>4410793050</v>
+        <v>4544760463</v>
+      </c>
+      <c r="D190" s="3">
+        <v>4086265237</v>
       </c>
       <c r="P190" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.2">
@@ -5711,10 +5516,13 @@
         <v>202</v>
       </c>
       <c r="B191" s="11">
-        <v>2474431127</v>
+        <v>3691843793</v>
+      </c>
+      <c r="C191" s="3">
+        <v>4544761808</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.2">
@@ -5722,16 +5530,16 @@
         <v>203</v>
       </c>
       <c r="B192" s="11">
-        <v>3691738336</v>
+        <v>3691844110</v>
       </c>
       <c r="C192" s="3">
-        <v>4544763211</v>
+        <v>4544758943</v>
       </c>
       <c r="D192" s="3">
-        <v>4086257096</v>
+        <v>4086264435</v>
       </c>
       <c r="P192" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.2">
@@ -5739,13 +5547,16 @@
         <v>204</v>
       </c>
       <c r="B193" s="11">
-        <v>3691841964</v>
+        <v>3691844929</v>
       </c>
       <c r="C193" s="3">
-        <v>4544759914</v>
+        <v>4544795636</v>
+      </c>
+      <c r="D193" s="3">
+        <v>4086268210</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.2">
@@ -5753,13 +5564,16 @@
         <v>205</v>
       </c>
       <c r="B194" s="11">
-        <v>3691844921</v>
+        <v>3691844839</v>
       </c>
       <c r="C194" s="3">
-        <v>4544759944</v>
+        <v>4544763919</v>
+      </c>
+      <c r="D194" s="3">
+        <v>4086269638</v>
       </c>
       <c r="P194" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.2">
@@ -5767,16 +5581,16 @@
         <v>206</v>
       </c>
       <c r="B195" s="11">
-        <v>3691842819</v>
-      </c>
-      <c r="C195" s="3">
-        <v>4544752572</v>
+        <v>3691843907</v>
+      </c>
+      <c r="C195" s="5">
+        <v>4544770164</v>
       </c>
       <c r="D195" s="3">
-        <v>4086258895</v>
+        <v>4086264553</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.2">
@@ -5784,16 +5598,16 @@
         <v>207</v>
       </c>
       <c r="B196" s="11">
-        <v>3691843282</v>
+        <v>3691843952</v>
       </c>
       <c r="C196" s="3">
-        <v>4544775205</v>
+        <v>4544769795</v>
       </c>
       <c r="D196" s="3">
-        <v>4086257286</v>
+        <v>4086264799</v>
       </c>
       <c r="P196" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.2">
@@ -5801,16 +5615,16 @@
         <v>208</v>
       </c>
       <c r="B197" s="11">
-        <v>3691843233</v>
+        <v>3691842650</v>
       </c>
       <c r="C197" s="3">
-        <v>4544751852</v>
+        <v>4544766143</v>
       </c>
       <c r="D197" s="3">
-        <v>4086260262</v>
+        <v>4086264238</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.2">
@@ -5818,16 +5632,16 @@
         <v>209</v>
       </c>
       <c r="B198" s="11">
-        <v>3691843824</v>
+        <v>3691843618</v>
       </c>
       <c r="C198" s="3">
-        <v>4544768940</v>
+        <v>4544765804</v>
       </c>
       <c r="D198" s="3">
-        <v>4086264776</v>
+        <v>4086264520</v>
       </c>
       <c r="P198" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="199" spans="1:16" x14ac:dyDescent="0.2">
@@ -5835,10 +5649,16 @@
         <v>210</v>
       </c>
       <c r="B199" s="11">
-        <v>3691843469</v>
+        <v>3691844620</v>
+      </c>
+      <c r="C199" s="3">
+        <v>4544756388</v>
+      </c>
+      <c r="D199" s="3">
+        <v>4086258042</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.2">
@@ -5846,16 +5666,16 @@
         <v>211</v>
       </c>
       <c r="B200" s="11">
-        <v>3691843333</v>
+        <v>3691842765</v>
       </c>
       <c r="C200" s="3">
-        <v>4544769486</v>
+        <v>4544754438</v>
       </c>
       <c r="D200" s="3">
-        <v>4086265043</v>
+        <v>4086263550</v>
       </c>
       <c r="P200" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="201" spans="1:16" x14ac:dyDescent="0.2">
@@ -5863,10 +5683,16 @@
         <v>212</v>
       </c>
       <c r="B201" s="11">
-        <v>3691843790</v>
+        <v>3691844111</v>
+      </c>
+      <c r="C201" s="5">
+        <v>4544761183</v>
+      </c>
+      <c r="D201" s="3">
+        <v>4086263588</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="202" spans="1:16" x14ac:dyDescent="0.2">
@@ -5874,16 +5700,16 @@
         <v>213</v>
       </c>
       <c r="B202" s="11">
-        <v>3691842613</v>
-      </c>
-      <c r="C202" s="3">
-        <v>4544760463</v>
+        <v>3691844304</v>
+      </c>
+      <c r="C202" s="5">
+        <v>4544774142</v>
       </c>
       <c r="D202" s="3">
-        <v>4086265237</v>
+        <v>4086265051</v>
       </c>
       <c r="P202" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.2">
@@ -5891,13 +5717,16 @@
         <v>214</v>
       </c>
       <c r="B203" s="11">
-        <v>3691843793</v>
+        <v>3691844657</v>
       </c>
       <c r="C203" s="3">
-        <v>4544761808</v>
+        <v>4544758784</v>
+      </c>
+      <c r="D203" s="3">
+        <v>4086263292</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.2">
@@ -5905,16 +5734,16 @@
         <v>215</v>
       </c>
       <c r="B204" s="11">
-        <v>3691844110</v>
+        <v>3691844061</v>
       </c>
       <c r="C204" s="3">
-        <v>4544758943</v>
+        <v>4544773289</v>
       </c>
       <c r="D204" s="3">
-        <v>4086264435</v>
+        <v>4086263416</v>
       </c>
       <c r="P204" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="205" spans="1:16" x14ac:dyDescent="0.2">
@@ -5922,16 +5751,16 @@
         <v>216</v>
       </c>
       <c r="B205" s="11">
-        <v>3691844929</v>
+        <v>3691843306</v>
       </c>
       <c r="C205" s="3">
-        <v>4544795636</v>
+        <v>4544757244</v>
       </c>
       <c r="D205" s="3">
-        <v>4086268210</v>
+        <v>4086258692</v>
       </c>
       <c r="P205" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="206" spans="1:16" x14ac:dyDescent="0.2">
@@ -5939,16 +5768,16 @@
         <v>217</v>
       </c>
       <c r="B206" s="11">
-        <v>3691844839</v>
+        <v>3691843846</v>
       </c>
       <c r="C206" s="3">
-        <v>4544763919</v>
+        <v>4544785851</v>
       </c>
       <c r="D206" s="3">
-        <v>4086269638</v>
+        <v>4086263152</v>
       </c>
       <c r="P206" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.2">
@@ -5956,16 +5785,16 @@
         <v>218</v>
       </c>
       <c r="B207" s="11">
-        <v>3691843907</v>
-      </c>
-      <c r="C207" s="5">
-        <v>4544770164</v>
+        <v>3691844082</v>
+      </c>
+      <c r="C207" s="3">
+        <v>4544764650</v>
       </c>
       <c r="D207" s="3">
-        <v>4086264553</v>
+        <v>4086266623</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.2">
@@ -5973,16 +5802,16 @@
         <v>219</v>
       </c>
       <c r="B208" s="11">
-        <v>3691843952</v>
+        <v>3691842493</v>
       </c>
       <c r="C208" s="3">
-        <v>4544769795</v>
+        <v>4544750975</v>
       </c>
       <c r="D208" s="3">
-        <v>4086264799</v>
+        <v>4086260019</v>
       </c>
       <c r="P208" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.2">
@@ -5990,16 +5819,16 @@
         <v>220</v>
       </c>
       <c r="B209" s="11">
-        <v>3691842650</v>
+        <v>3691843045</v>
       </c>
       <c r="C209" s="3">
-        <v>4544766143</v>
+        <v>4544767981</v>
       </c>
       <c r="D209" s="3">
-        <v>4086264238</v>
+        <v>4431489467</v>
       </c>
       <c r="P209" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.2">
@@ -6007,16 +5836,13 @@
         <v>221</v>
       </c>
       <c r="B210" s="11">
-        <v>3691843618</v>
+        <v>3697385068</v>
       </c>
       <c r="C210" s="3">
-        <v>4544765804</v>
-      </c>
-      <c r="D210" s="3">
-        <v>4086264520</v>
+        <v>4544768974</v>
       </c>
       <c r="P210" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.2">
@@ -6024,16 +5850,16 @@
         <v>222</v>
       </c>
       <c r="B211" s="11">
-        <v>3691844620</v>
+        <v>3697386937</v>
       </c>
       <c r="C211" s="3">
-        <v>4544756388</v>
+        <v>4544772744</v>
       </c>
       <c r="D211" s="3">
-        <v>4086258042</v>
+        <v>4086264493</v>
       </c>
       <c r="P211" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.2">
@@ -6041,16 +5867,13 @@
         <v>223</v>
       </c>
       <c r="B212" s="11">
-        <v>3691842765</v>
+        <v>3697377718</v>
       </c>
       <c r="C212" s="3">
-        <v>4544754438</v>
-      </c>
-      <c r="D212" s="3">
-        <v>4086263550</v>
+        <v>4544751038</v>
       </c>
       <c r="P212" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.2">
@@ -6058,16 +5881,16 @@
         <v>224</v>
       </c>
       <c r="B213" s="11">
-        <v>3691844111</v>
-      </c>
-      <c r="C213" s="5">
-        <v>4544761183</v>
+        <v>3697386081</v>
+      </c>
+      <c r="C213" s="3">
+        <v>4544756093</v>
       </c>
       <c r="D213" s="3">
-        <v>4086263588</v>
+        <v>4086258905</v>
       </c>
       <c r="P213" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.2">
@@ -6075,16 +5898,16 @@
         <v>225</v>
       </c>
       <c r="B214" s="11">
-        <v>3691844304</v>
-      </c>
-      <c r="C214" s="5">
-        <v>4544774142</v>
+        <v>3697386923</v>
+      </c>
+      <c r="C214" s="3">
+        <v>4544752786</v>
       </c>
       <c r="D214" s="3">
-        <v>4086265051</v>
+        <v>4086265396</v>
       </c>
       <c r="P214" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.2">
@@ -6092,16 +5915,16 @@
         <v>226</v>
       </c>
       <c r="B215" s="11">
-        <v>3691844657</v>
+        <v>3697385185</v>
       </c>
       <c r="C215" s="3">
-        <v>4544758784</v>
+        <v>4544784694</v>
       </c>
       <c r="D215" s="3">
-        <v>4086263292</v>
+        <v>4086263559</v>
       </c>
       <c r="P215" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.2">
@@ -6109,16 +5932,16 @@
         <v>227</v>
       </c>
       <c r="B216" s="11">
-        <v>3691844061</v>
+        <v>3697385622</v>
       </c>
       <c r="C216" s="3">
-        <v>4544773289</v>
+        <v>4544769648</v>
       </c>
       <c r="D216" s="3">
-        <v>4086263416</v>
+        <v>4086263717</v>
       </c>
       <c r="P216" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.2">
@@ -6126,16 +5949,16 @@
         <v>228</v>
       </c>
       <c r="B217" s="11">
-        <v>3691843306</v>
+        <v>3697387116</v>
       </c>
       <c r="C217" s="3">
-        <v>4544757244</v>
+        <v>4544764615</v>
       </c>
       <c r="D217" s="3">
-        <v>4086258692</v>
+        <v>4086266543</v>
       </c>
       <c r="P217" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.2">
@@ -6143,16 +5966,16 @@
         <v>229</v>
       </c>
       <c r="B218" s="11">
-        <v>3691843846</v>
+        <v>3697378793</v>
       </c>
       <c r="C218" s="3">
-        <v>4544785851</v>
+        <v>4544756164</v>
       </c>
       <c r="D218" s="3">
-        <v>4086263152</v>
+        <v>4086258058</v>
       </c>
       <c r="P218" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.2">
@@ -6160,16 +5983,16 @@
         <v>230</v>
       </c>
       <c r="B219" s="11">
-        <v>3691844082</v>
+        <v>3697384946</v>
       </c>
       <c r="C219" s="3">
-        <v>4544764650</v>
+        <v>4544764972</v>
       </c>
       <c r="D219" s="3">
-        <v>4086266623</v>
+        <v>4086268182</v>
       </c>
       <c r="P219" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.2">
@@ -6177,16 +6000,13 @@
         <v>231</v>
       </c>
       <c r="B220" s="11">
-        <v>3691842493</v>
+        <v>3697385546</v>
       </c>
       <c r="C220" s="3">
-        <v>4544750975</v>
-      </c>
-      <c r="D220" s="3">
-        <v>4086260019</v>
+        <v>4544771182</v>
       </c>
       <c r="P220" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.2">
@@ -6194,16 +6014,16 @@
         <v>232</v>
       </c>
       <c r="B221" s="11">
-        <v>3691843045</v>
+        <v>3697386517</v>
       </c>
       <c r="C221" s="3">
-        <v>4544767981</v>
+        <v>4544752337</v>
       </c>
       <c r="D221" s="3">
-        <v>4431489467</v>
+        <v>4086258252</v>
       </c>
       <c r="P221" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.2">
@@ -6211,13 +6031,10 @@
         <v>233</v>
       </c>
       <c r="B222" s="11">
-        <v>3697385068</v>
-      </c>
-      <c r="C222" s="3">
-        <v>4544768974</v>
+        <v>3697385469</v>
       </c>
       <c r="P222" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.2">
@@ -6225,16 +6042,16 @@
         <v>234</v>
       </c>
       <c r="B223" s="11">
-        <v>3697386937</v>
+        <v>3697386057</v>
       </c>
       <c r="C223" s="3">
-        <v>4544772744</v>
+        <v>4544751072</v>
       </c>
       <c r="D223" s="3">
-        <v>4086264493</v>
+        <v>4086259075</v>
       </c>
       <c r="P223" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.2">
@@ -6242,13 +6059,16 @@
         <v>235</v>
       </c>
       <c r="B224" s="11">
-        <v>3697377718</v>
+        <v>3697386822</v>
       </c>
       <c r="C224" s="3">
-        <v>4544751038</v>
+        <v>4544773906</v>
+      </c>
+      <c r="D224" s="3">
+        <v>4086264413</v>
       </c>
       <c r="P224" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.2">
@@ -6256,16 +6076,13 @@
         <v>236</v>
       </c>
       <c r="B225" s="11">
-        <v>3697386081</v>
+        <v>3697386529</v>
       </c>
       <c r="C225" s="3">
-        <v>4544756093</v>
-      </c>
-      <c r="D225" s="3">
-        <v>4086258905</v>
+        <v>4544765611</v>
       </c>
       <c r="P225" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.2">
@@ -6273,16 +6090,16 @@
         <v>237</v>
       </c>
       <c r="B226" s="11">
-        <v>3697386923</v>
+        <v>3697385541</v>
       </c>
       <c r="C226" s="3">
-        <v>4544752786</v>
+        <v>4544751311</v>
       </c>
       <c r="D226" s="3">
-        <v>4086265396</v>
+        <v>4086258395</v>
       </c>
       <c r="P226" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.2">
@@ -6290,16 +6107,16 @@
         <v>238</v>
       </c>
       <c r="B227" s="11">
-        <v>3697385185</v>
+        <v>3697384880</v>
       </c>
       <c r="C227" s="3">
-        <v>4544784694</v>
+        <v>4544750231</v>
       </c>
       <c r="D227" s="3">
-        <v>4086263559</v>
+        <v>4086258367</v>
       </c>
       <c r="P227" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.2">
@@ -6307,16 +6124,16 @@
         <v>239</v>
       </c>
       <c r="B228" s="11">
-        <v>3697385622</v>
+        <v>3697386735</v>
       </c>
       <c r="C228" s="3">
-        <v>4544769648</v>
+        <v>4544764030</v>
       </c>
       <c r="D228" s="3">
-        <v>4086263717</v>
+        <v>4086263561</v>
       </c>
       <c r="P228" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.2">
@@ -6324,16 +6141,16 @@
         <v>240</v>
       </c>
       <c r="B229" s="11">
-        <v>3697387116</v>
+        <v>3697386369</v>
       </c>
       <c r="C229" s="3">
-        <v>4544764615</v>
+        <v>4544766492</v>
       </c>
       <c r="D229" s="3">
-        <v>4086266543</v>
+        <v>4086268091</v>
       </c>
       <c r="P229" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.2">
@@ -6341,16 +6158,16 @@
         <v>241</v>
       </c>
       <c r="B230" s="11">
-        <v>3697378793</v>
+        <v>3697386368</v>
       </c>
       <c r="C230" s="3">
-        <v>4544756164</v>
+        <v>4544769576</v>
       </c>
       <c r="D230" s="3">
-        <v>4086258058</v>
+        <v>4086269800</v>
       </c>
       <c r="P230" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.2">
@@ -6358,16 +6175,16 @@
         <v>242</v>
       </c>
       <c r="B231" s="11">
-        <v>3697384946</v>
+        <v>3697384419</v>
       </c>
       <c r="C231" s="3">
-        <v>4544764972</v>
+        <v>4544793634</v>
       </c>
       <c r="D231" s="3">
-        <v>4086268182</v>
+        <v>4086263881</v>
       </c>
       <c r="P231" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.2">
@@ -6375,13 +6192,16 @@
         <v>243</v>
       </c>
       <c r="B232" s="11">
-        <v>3697385546</v>
+        <v>3697386364</v>
       </c>
       <c r="C232" s="3">
-        <v>4544771182</v>
+        <v>4544773857</v>
+      </c>
+      <c r="D232" s="3">
+        <v>4086270302</v>
       </c>
       <c r="P232" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.2">
@@ -6389,16 +6209,13 @@
         <v>244</v>
       </c>
       <c r="B233" s="11">
-        <v>3697386517</v>
+        <v>3697386666</v>
       </c>
       <c r="C233" s="3">
-        <v>4544752337</v>
-      </c>
-      <c r="D233" s="3">
-        <v>4086258252</v>
+        <v>4544772762</v>
       </c>
       <c r="P233" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.2">
@@ -6406,10 +6223,16 @@
         <v>245</v>
       </c>
       <c r="B234" s="11">
-        <v>3697385469</v>
+        <v>3697386325</v>
+      </c>
+      <c r="C234" s="3">
+        <v>4544768478</v>
+      </c>
+      <c r="D234" s="3">
+        <v>4086264843</v>
       </c>
       <c r="P234" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.2">
@@ -6417,16 +6240,16 @@
         <v>246</v>
       </c>
       <c r="B235" s="11">
-        <v>3697386057</v>
+        <v>3697387233</v>
       </c>
       <c r="C235" s="3">
-        <v>4544751072</v>
+        <v>4544763082</v>
       </c>
       <c r="D235" s="3">
-        <v>4086259075</v>
+        <v>4086263739</v>
       </c>
       <c r="P235" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.2">
@@ -6434,16 +6257,16 @@
         <v>247</v>
       </c>
       <c r="B236" s="11">
-        <v>3697386822</v>
+        <v>3697386036</v>
       </c>
       <c r="C236" s="3">
-        <v>4544773906</v>
+        <v>4544772750</v>
       </c>
       <c r="D236" s="3">
-        <v>4086264413</v>
+        <v>4086263993</v>
       </c>
       <c r="P236" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.2">
@@ -6451,13 +6274,13 @@
         <v>248</v>
       </c>
       <c r="B237" s="11">
-        <v>3697386529</v>
+        <v>3697387185</v>
       </c>
       <c r="C237" s="3">
-        <v>4544765611</v>
+        <v>4544771769</v>
       </c>
       <c r="P237" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.2">
@@ -6465,16 +6288,16 @@
         <v>249</v>
       </c>
       <c r="B238" s="11">
-        <v>3697385541</v>
+        <v>3697387392</v>
       </c>
       <c r="C238" s="3">
-        <v>4544751311</v>
+        <v>4544763326</v>
       </c>
       <c r="D238" s="3">
-        <v>4086258395</v>
+        <v>4086268414</v>
       </c>
       <c r="P238" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
@@ -6482,16 +6305,16 @@
         <v>250</v>
       </c>
       <c r="B239" s="11">
-        <v>3697384880</v>
-      </c>
-      <c r="C239" s="3">
-        <v>4544750231</v>
+        <v>3697504349</v>
+      </c>
+      <c r="C239" s="5">
+        <v>4544751665</v>
       </c>
       <c r="D239" s="3">
-        <v>4086258367</v>
+        <v>4086258111</v>
       </c>
       <c r="P239" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.2">
@@ -6499,16 +6322,16 @@
         <v>251</v>
       </c>
       <c r="B240" s="11">
-        <v>3697386735</v>
+        <v>3697505185</v>
       </c>
       <c r="C240" s="3">
-        <v>4544764030</v>
+        <v>4544771540</v>
       </c>
       <c r="D240" s="3">
-        <v>4086263561</v>
+        <v>4086264061</v>
       </c>
       <c r="P240" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
@@ -6516,16 +6339,16 @@
         <v>252</v>
       </c>
       <c r="B241" s="11">
-        <v>3697386369</v>
+        <v>3697504278</v>
       </c>
       <c r="C241" s="3">
-        <v>4544766492</v>
+        <v>4544763195</v>
       </c>
       <c r="D241" s="3">
-        <v>4086268091</v>
+        <v>4086265130</v>
       </c>
       <c r="P241" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.2">
@@ -6533,16 +6356,16 @@
         <v>253</v>
       </c>
       <c r="B242" s="11">
-        <v>3697386368</v>
+        <v>3697504906</v>
       </c>
       <c r="C242" s="3">
-        <v>4544769576</v>
+        <v>4544763916</v>
       </c>
       <c r="D242" s="3">
-        <v>4086269800</v>
+        <v>4086268682</v>
       </c>
       <c r="P242" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
@@ -6550,16 +6373,16 @@
         <v>254</v>
       </c>
       <c r="B243" s="11">
-        <v>3697384419</v>
+        <v>3697505720</v>
       </c>
       <c r="C243" s="3">
-        <v>4544793634</v>
+        <v>4544753127</v>
       </c>
       <c r="D243" s="3">
-        <v>4086263881</v>
+        <v>4086257798</v>
       </c>
       <c r="P243" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.2">
@@ -6567,16 +6390,16 @@
         <v>255</v>
       </c>
       <c r="B244" s="11">
-        <v>3697386364</v>
+        <v>3697505355</v>
       </c>
       <c r="C244" s="3">
-        <v>4544773857</v>
+        <v>4544770182</v>
       </c>
       <c r="D244" s="3">
-        <v>4086270302</v>
+        <v>4086265449</v>
       </c>
       <c r="P244" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.2">
@@ -6584,13 +6407,13 @@
         <v>256</v>
       </c>
       <c r="B245" s="11">
-        <v>3697386666</v>
+        <v>3697504484</v>
       </c>
       <c r="C245" s="3">
-        <v>4544772762</v>
+        <v>4544759886</v>
       </c>
       <c r="P245" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.2">
@@ -6598,16 +6421,16 @@
         <v>257</v>
       </c>
       <c r="B246" s="11">
-        <v>3697386325</v>
+        <v>3697504162</v>
       </c>
       <c r="C246" s="3">
-        <v>4544768478</v>
+        <v>4544768205</v>
       </c>
       <c r="D246" s="3">
-        <v>4086264843</v>
+        <v>4086267459</v>
       </c>
       <c r="P246" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.2">
@@ -6615,16 +6438,16 @@
         <v>258</v>
       </c>
       <c r="B247" s="11">
-        <v>3697387233</v>
+        <v>3697505218</v>
       </c>
       <c r="C247" s="3">
-        <v>4544763082</v>
+        <v>4544768630</v>
       </c>
       <c r="D247" s="3">
-        <v>4086263739</v>
+        <v>4086266739</v>
       </c>
       <c r="P247" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.2">
@@ -6632,16 +6455,13 @@
         <v>259</v>
       </c>
       <c r="B248" s="11">
-        <v>3697386036</v>
+        <v>3697505811</v>
       </c>
       <c r="C248" s="3">
-        <v>4544772750</v>
-      </c>
-      <c r="D248" s="3">
-        <v>4086263993</v>
+        <v>4544790815</v>
       </c>
       <c r="P248" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.2">
@@ -6649,13 +6469,13 @@
         <v>260</v>
       </c>
       <c r="B249" s="11">
-        <v>3697387185</v>
+        <v>3697504168</v>
       </c>
       <c r="C249" s="3">
-        <v>4544771769</v>
+        <v>4544759610</v>
       </c>
       <c r="P249" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.2">
@@ -6663,16 +6483,16 @@
         <v>261</v>
       </c>
       <c r="B250" s="11">
-        <v>3697387392</v>
+        <v>3697504479</v>
       </c>
       <c r="C250" s="3">
-        <v>4544763326</v>
+        <v>4544773237</v>
       </c>
       <c r="D250" s="3">
-        <v>4086268414</v>
+        <v>4086265504</v>
       </c>
       <c r="P250" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.2">
@@ -6680,16 +6500,16 @@
         <v>262</v>
       </c>
       <c r="B251" s="11">
-        <v>3697504349</v>
-      </c>
-      <c r="C251" s="5">
-        <v>4544751665</v>
+        <v>3697504448</v>
+      </c>
+      <c r="C251" s="3">
+        <v>4544761414</v>
       </c>
       <c r="D251" s="3">
-        <v>4086258111</v>
+        <v>4086265129</v>
       </c>
       <c r="P251" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.2">
@@ -6697,16 +6517,16 @@
         <v>263</v>
       </c>
       <c r="B252" s="11">
-        <v>3697505185</v>
+        <v>3697504613</v>
       </c>
       <c r="C252" s="3">
-        <v>4544771540</v>
+        <v>4544762268</v>
       </c>
       <c r="D252" s="3">
-        <v>4086264061</v>
+        <v>4086263860</v>
       </c>
       <c r="P252" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.2">
@@ -6714,16 +6534,13 @@
         <v>264</v>
       </c>
       <c r="B253" s="11">
-        <v>3697504278</v>
-      </c>
-      <c r="C253" s="3">
-        <v>4544763195</v>
-      </c>
-      <c r="D253" s="3">
-        <v>4086265130</v>
+        <v>3697504303</v>
+      </c>
+      <c r="C253" s="5">
+        <v>4544762172</v>
       </c>
       <c r="P253" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.2">
@@ -6731,16 +6548,13 @@
         <v>265</v>
       </c>
       <c r="B254" s="11">
-        <v>3697504906</v>
+        <v>3697504999</v>
       </c>
       <c r="C254" s="3">
-        <v>4544763916</v>
-      </c>
-      <c r="D254" s="3">
-        <v>4086268682</v>
+        <v>4544769643</v>
       </c>
       <c r="P254" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.2">
@@ -6748,16 +6562,16 @@
         <v>266</v>
       </c>
       <c r="B255" s="11">
-        <v>3697505720</v>
+        <v>3697505659</v>
       </c>
       <c r="C255" s="3">
-        <v>4544753127</v>
+        <v>4544752647</v>
       </c>
       <c r="D255" s="3">
-        <v>4086257798</v>
+        <v>4086258729</v>
       </c>
       <c r="P255" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.2">
@@ -6765,16 +6579,16 @@
         <v>267</v>
       </c>
       <c r="B256" s="11">
-        <v>3697505355</v>
+        <v>3697504347</v>
       </c>
       <c r="C256" s="3">
-        <v>4544770182</v>
+        <v>4544765324</v>
       </c>
       <c r="D256" s="3">
-        <v>4086265449</v>
+        <v>4086263587</v>
       </c>
       <c r="P256" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.2">
@@ -6782,13 +6596,16 @@
         <v>268</v>
       </c>
       <c r="B257" s="11">
-        <v>3697504484</v>
+        <v>3697504996</v>
       </c>
       <c r="C257" s="3">
-        <v>4544759886</v>
+        <v>4544751070</v>
+      </c>
+      <c r="D257" s="3">
+        <v>4086258113</v>
       </c>
       <c r="P257" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.2">
@@ -6796,16 +6613,16 @@
         <v>269</v>
       </c>
       <c r="B258" s="11">
-        <v>3697504162</v>
+        <v>3697504363</v>
       </c>
       <c r="C258" s="3">
-        <v>4544768205</v>
+        <v>4544772670</v>
       </c>
       <c r="D258" s="3">
-        <v>4086267459</v>
+        <v>4086264485</v>
       </c>
       <c r="P258" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.2">
@@ -6813,16 +6630,16 @@
         <v>270</v>
       </c>
       <c r="B259" s="11">
-        <v>3697505218</v>
+        <v>3697505978</v>
       </c>
       <c r="C259" s="3">
-        <v>4544768630</v>
+        <v>4544754261</v>
       </c>
       <c r="D259" s="3">
-        <v>4086266739</v>
+        <v>4086258409</v>
       </c>
       <c r="P259" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.2">
@@ -6830,13 +6647,16 @@
         <v>271</v>
       </c>
       <c r="B260" s="11">
-        <v>3697505811</v>
+        <v>3697504998</v>
       </c>
       <c r="C260" s="3">
-        <v>4544790815</v>
+        <v>4544751992</v>
+      </c>
+      <c r="D260" s="3">
+        <v>4086257806</v>
       </c>
       <c r="P260" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.2">
@@ -6844,13 +6664,16 @@
         <v>272</v>
       </c>
       <c r="B261" s="11">
-        <v>3697504168</v>
+        <v>3697504814</v>
       </c>
       <c r="C261" s="3">
-        <v>4544759610</v>
+        <v>4544754507</v>
+      </c>
+      <c r="D261" s="3">
+        <v>4086260890</v>
       </c>
       <c r="P261" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="262" spans="1:16" x14ac:dyDescent="0.2">
@@ -6858,16 +6681,16 @@
         <v>273</v>
       </c>
       <c r="B262" s="11">
-        <v>3697504479</v>
+        <v>3697505764</v>
       </c>
       <c r="C262" s="3">
-        <v>4544773237</v>
+        <v>4544758228</v>
       </c>
       <c r="D262" s="3">
-        <v>4086265504</v>
+        <v>4086258137</v>
       </c>
       <c r="P262" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="263" spans="1:16" x14ac:dyDescent="0.2">
@@ -6875,16 +6698,16 @@
         <v>274</v>
       </c>
       <c r="B263" s="11">
-        <v>3697504448</v>
+        <v>3697506004</v>
       </c>
       <c r="C263" s="3">
-        <v>4544761414</v>
+        <v>4544753701</v>
       </c>
       <c r="D263" s="3">
-        <v>4086265129</v>
+        <v>4086258803</v>
       </c>
       <c r="P263" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="264" spans="1:16" x14ac:dyDescent="0.2">
@@ -6892,16 +6715,16 @@
         <v>275</v>
       </c>
       <c r="B264" s="11">
-        <v>3697504613</v>
+        <v>3697505436</v>
       </c>
       <c r="C264" s="3">
-        <v>4544762268</v>
+        <v>4544756409</v>
       </c>
       <c r="D264" s="3">
-        <v>4086263860</v>
+        <v>4086259664</v>
       </c>
       <c r="P264" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.2">
@@ -6909,13 +6732,13 @@
         <v>276</v>
       </c>
       <c r="B265" s="11">
-        <v>3697504303</v>
-      </c>
-      <c r="C265" s="5">
-        <v>4544762172</v>
+        <v>3697504812</v>
+      </c>
+      <c r="C265" s="3">
+        <v>4086258183</v>
       </c>
       <c r="P265" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="266" spans="1:16" x14ac:dyDescent="0.2">
@@ -6923,13 +6746,13 @@
         <v>277</v>
       </c>
       <c r="B266" s="11">
-        <v>3697504999</v>
+        <v>3697505575</v>
       </c>
       <c r="C266" s="3">
-        <v>4544769643</v>
+        <v>4544764731</v>
       </c>
       <c r="P266" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="267" spans="1:16" x14ac:dyDescent="0.2">
@@ -6937,211 +6760,13 @@
         <v>278</v>
       </c>
       <c r="B267" s="11">
-        <v>3697505659</v>
+        <v>3701081855</v>
       </c>
       <c r="C267" s="3">
-        <v>4544752647</v>
-      </c>
-      <c r="D267" s="3">
-        <v>4086258729</v>
+        <v>4544763258</v>
       </c>
       <c r="P267" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A268" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B268" s="11">
-        <v>3697504347</v>
-      </c>
-      <c r="C268" s="3">
-        <v>4544765324</v>
-      </c>
-      <c r="D268" s="3">
-        <v>4086263587</v>
-      </c>
-      <c r="P268" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A269" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B269" s="11">
-        <v>3697504996</v>
-      </c>
-      <c r="C269" s="3">
-        <v>4544751070</v>
-      </c>
-      <c r="D269" s="3">
-        <v>4086258113</v>
-      </c>
-      <c r="P269" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A270" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B270" s="11">
-        <v>3697504363</v>
-      </c>
-      <c r="C270" s="3">
-        <v>4544772670</v>
-      </c>
-      <c r="D270" s="3">
-        <v>4086264485</v>
-      </c>
-      <c r="P270" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A271" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B271" s="11">
-        <v>3697505978</v>
-      </c>
-      <c r="C271" s="3">
-        <v>4544754261</v>
-      </c>
-      <c r="D271" s="3">
-        <v>4086258409</v>
-      </c>
-      <c r="P271" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A272" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B272" s="11">
-        <v>3697504998</v>
-      </c>
-      <c r="C272" s="3">
-        <v>4544751992</v>
-      </c>
-      <c r="D272" s="3">
-        <v>4086257806</v>
-      </c>
-      <c r="P272" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A273" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B273" s="11">
-        <v>3697504814</v>
-      </c>
-      <c r="C273" s="3">
-        <v>4544754507</v>
-      </c>
-      <c r="D273" s="3">
-        <v>4086260890</v>
-      </c>
-      <c r="P273" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A274" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B274" s="11">
-        <v>3697505764</v>
-      </c>
-      <c r="C274" s="3">
-        <v>4544758228</v>
-      </c>
-      <c r="D274" s="3">
-        <v>4086258137</v>
-      </c>
-      <c r="P274" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A275" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B275" s="11">
-        <v>3697506004</v>
-      </c>
-      <c r="C275" s="3">
-        <v>4544753701</v>
-      </c>
-      <c r="D275" s="3">
-        <v>4086258803</v>
-      </c>
-      <c r="P275" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A276" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B276" s="11">
-        <v>3697505436</v>
-      </c>
-      <c r="C276" s="3">
-        <v>4544756409</v>
-      </c>
-      <c r="D276" s="3">
-        <v>4086259664</v>
-      </c>
-      <c r="P276" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A277" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B277" s="11">
-        <v>3697504812</v>
-      </c>
-      <c r="C277" s="3">
-        <v>4086258183</v>
-      </c>
-      <c r="P277" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A278" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B278" s="11">
-        <v>3697505575</v>
-      </c>
-      <c r="C278" s="3">
-        <v>4544764731</v>
-      </c>
-      <c r="P278" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A279" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B279" s="11">
-        <v>3701081855</v>
-      </c>
-      <c r="C279" s="3">
-        <v>4544763258</v>
-      </c>
-      <c r="P279" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
